--- a/artfynd/Maskaure Renskötartjärnen, 8,3 ha artfynd.xlsx
+++ b/artfynd/Maskaure Renskötartjärnen, 8,3 ha artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY80"/>
+  <dimension ref="A1:AY81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2255,48 +2255,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>96019500</v>
+        <v>135326001</v>
       </c>
       <c r="B18" t="n">
-        <v>78993</v>
+        <v>92201</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>353</v>
+        <v>67</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Seitejaure, Pi lm</t>
+          <t>Maskaure Renskötartjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>617548</v>
+        <v>617442</v>
       </c>
       <c r="R18" t="n">
-        <v>7315810</v>
+        <v>7315781</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2320,12 +2320,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2334,25 +2344,30 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Julian Klein</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Julian Klein, Barbara Kühn, Björn Mildh, Kristina Bäck, Isak Vahlström, Maj Aspebo</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>96194508</v>
+        <v>96019500</v>
       </c>
       <c r="B19" t="n">
         <v>78993</v>
@@ -2387,13 +2402,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>617483</v>
+        <v>617548</v>
       </c>
       <c r="R19" t="n">
-        <v>7315870</v>
+        <v>7315810</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2437,22 +2452,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Julian Klein</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Barbara Kühn, Julian Klein, Björn Mildh, Kristina Bäck, Maj Aspebo</t>
+          <t>Julian Klein, Barbara Kühn, Björn Mildh, Kristina Bäck, Isak Vahlström, Maj Aspebo</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135322911</v>
+        <v>96194508</v>
       </c>
       <c r="B20" t="n">
-        <v>79039</v>
+        <v>78993</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2480,17 +2495,17 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Renskötartjärnen, Pi lm</t>
+          <t>Seitejaure, Pi lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>617418</v>
+        <v>617483</v>
       </c>
       <c r="R20" t="n">
-        <v>7315875</v>
+        <v>7315870</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2514,22 +2529,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>14:49</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>14:49</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2544,23 +2549,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Isak Vahlström, Barbara Kühn, Julian Klein, Björn Mildh, Kristina Bäck, Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135322923</v>
+        <v>135322911</v>
       </c>
       <c r="B21" t="n">
         <v>79039</v>
@@ -2595,10 +2596,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>617395</v>
+        <v>617418</v>
       </c>
       <c r="R21" t="n">
-        <v>7315778</v>
+        <v>7315875</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2630,7 +2631,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2640,7 +2641,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2671,7 +2672,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135323509</v>
+        <v>135322923</v>
       </c>
       <c r="B22" t="n">
         <v>79039</v>
@@ -2700,19 +2701,16 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran SV + Renskötartjärnen_topo, Pi lm</t>
+          <t>Renskötartjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>617488</v>
+        <v>617395</v>
       </c>
       <c r="R22" t="n">
-        <v>7315863</v>
+        <v>7315778</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2744,7 +2742,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2754,7 +2752,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2763,19 +2761,18 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2786,7 +2783,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135323514</v>
+        <v>135323509</v>
       </c>
       <c r="B23" t="n">
         <v>79039</v>
@@ -2815,19 +2812,22 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Maskaure Långmyran SV + Renskötartjärnen_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>617617</v>
+        <v>617488</v>
       </c>
       <c r="R23" t="n">
-        <v>7315754</v>
+        <v>7315863</v>
       </c>
       <c r="S23" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2875,6 +2875,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2889,11 +2890,15 @@
           <t>Cecilia Goldkuhl</t>
         </is>
       </c>
-      <c r="AY23" t="inlineStr"/>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135330900</v>
+        <v>135323514</v>
       </c>
       <c r="B24" t="n">
         <v>79039</v>
@@ -2924,17 +2929,17 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran SV + Renskötartjärnen, Pi lm</t>
+          <t>Maskaure Långmyran SV + Renskötartjärnen_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>617490</v>
+        <v>617617</v>
       </c>
       <c r="R24" t="n">
-        <v>7315847</v>
+        <v>7315754</v>
       </c>
       <c r="S24" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2963,7 +2968,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -2973,7 +2978,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2988,64 +2993,60 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Johan Råghall, Cecilia Goldkuhl, per-erik mukka, Christina Boyd, Moa Turid Lövdahl</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>96194504</v>
+        <v>135330900</v>
       </c>
       <c r="B25" t="n">
-        <v>91846</v>
+        <v>79039</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>714</v>
+        <v>353</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tallstocksticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Osmoporus protractus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Bondartsev</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Seitejaure, Pi lm</t>
+          <t>Maskaure Långmyran SV + Renskötartjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>617476</v>
+        <v>617490</v>
       </c>
       <c r="R25" t="n">
-        <v>7315870</v>
+        <v>7315847</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3069,12 +3070,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3089,22 +3100,26 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Barbara Kühn, Julian Klein, Björn Mildh, Kristina Bäck, Maj Aspebo</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
+          <t>Elin Kannerby, Johan Råghall, Cecilia Goldkuhl, per-erik mukka, Christina Boyd, Moa Turid Lövdahl</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>96019487</v>
+        <v>96194504</v>
       </c>
       <c r="B26" t="n">
-        <v>91923</v>
+        <v>91846</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3112,21 +3127,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1204</v>
+        <v>714</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tallstocksticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Osmoporus protractus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3136,13 +3151,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>617546</v>
+        <v>617476</v>
       </c>
       <c r="R26" t="n">
-        <v>7315805</v>
+        <v>7315870</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3186,19 +3201,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Julian Klein</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Julian Klein, Barbara Kühn, Björn Mildh, Kristina Bäck, Isak Vahlström, Maj Aspebo</t>
+          <t>Isak Vahlström, Barbara Kühn, Julian Klein, Björn Mildh, Kristina Bäck, Maj Aspebo</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>96194507</v>
+        <v>96019487</v>
       </c>
       <c r="B27" t="n">
         <v>91923</v>
@@ -3233,13 +3248,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>617476</v>
+        <v>617546</v>
       </c>
       <c r="R27" t="n">
-        <v>7315870</v>
+        <v>7315805</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3283,22 +3298,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Julian Klein</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Barbara Kühn, Julian Klein, Björn Mildh, Kristina Bäck, Maj Aspebo</t>
+          <t>Julian Klein, Barbara Kühn, Björn Mildh, Kristina Bäck, Isak Vahlström, Maj Aspebo</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>96194502</v>
+        <v>96194507</v>
       </c>
       <c r="B28" t="n">
-        <v>92083</v>
+        <v>91923</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3306,21 +3321,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1503</v>
+        <v>1204</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3330,10 +3345,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>617497</v>
+        <v>617476</v>
       </c>
       <c r="R28" t="n">
-        <v>7315828</v>
+        <v>7315870</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3392,7 +3407,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>96194509</v>
+        <v>96194502</v>
       </c>
       <c r="B29" t="n">
         <v>92083</v>
@@ -3427,10 +3442,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>617398</v>
+        <v>617497</v>
       </c>
       <c r="R29" t="n">
-        <v>7315856</v>
+        <v>7315828</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3489,10 +3504,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135329747</v>
+        <v>96194509</v>
       </c>
       <c r="B30" t="n">
-        <v>92153</v>
+        <v>92083</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3520,17 +3535,17 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>_Maskaure Långmyran SV + Renskötartjärnen_topo, Pi lm</t>
+          <t>Seitejaure, Pi lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>617572</v>
+        <v>617398</v>
       </c>
       <c r="R30" t="n">
-        <v>7315630</v>
+        <v>7315856</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3554,27 +3569,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>15:15</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Tallåga</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3589,23 +3589,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Moa Turid Lövdahl</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Moa Turid Lövdahl</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Isak Vahlström, Barbara Kühn, Julian Klein, Björn Mildh, Kristina Bäck, Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135330904</v>
+        <v>135329747</v>
       </c>
       <c r="B31" t="n">
         <v>92153</v>
@@ -3636,17 +3632,17 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran SV + Renskötartjärnen, Pi lm</t>
+          <t>_Maskaure Långmyran SV + Renskötartjärnen_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>617575</v>
+        <v>617572</v>
       </c>
       <c r="R31" t="n">
-        <v>7315628</v>
+        <v>7315630</v>
       </c>
       <c r="S31" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3675,7 +3671,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3685,7 +3681,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Tallåga</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3700,12 +3701,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Moa Turid Lövdahl</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Johan Råghall, Cecilia Goldkuhl, per-erik mukka, Christina Boyd, Moa Turid Lövdahl</t>
+          <t>Moa Turid Lövdahl</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3716,48 +3717,48 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>96194505</v>
+        <v>135330904</v>
       </c>
       <c r="B32" t="n">
-        <v>91962</v>
+        <v>92153</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2079</v>
+        <v>1503</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Seitejaure, Pi lm</t>
+          <t>Maskaure Långmyran SV + Renskötartjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>617476</v>
+        <v>617575</v>
       </c>
       <c r="R32" t="n">
-        <v>7315870</v>
+        <v>7315628</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3781,12 +3782,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3801,22 +3812,26 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Barbara Kühn, Julian Klein, Björn Mildh, Kristina Bäck, Maj Aspebo</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr"/>
+          <t>Elin Kannerby, Johan Råghall, Cecilia Goldkuhl, per-erik mukka, Christina Boyd, Moa Turid Lövdahl</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135323512</v>
+        <v>96194505</v>
       </c>
       <c r="B33" t="n">
-        <v>92027</v>
+        <v>91962</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3844,17 +3859,17 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran SV + Renskötartjärnen_topo, Pi lm</t>
+          <t>Seitejaure, Pi lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>617601</v>
+        <v>617476</v>
       </c>
       <c r="R33" t="n">
-        <v>7315777</v>
+        <v>7315870</v>
       </c>
       <c r="S33" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3878,22 +3893,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>15:05</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>15:05</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3908,19 +3913,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Isak Vahlström, Barbara Kühn, Julian Klein, Björn Mildh, Kristina Bäck, Maj Aspebo</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135330905</v>
+        <v>135323512</v>
       </c>
       <c r="B34" t="n">
         <v>92027</v>
@@ -3951,17 +3956,17 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran SV + Renskötartjärnen, Pi lm</t>
+          <t>Maskaure Långmyran SV + Renskötartjärnen_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>617574</v>
+        <v>617601</v>
       </c>
       <c r="R34" t="n">
-        <v>7315632</v>
+        <v>7315777</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3990,7 +3995,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4000,7 +4005,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4015,26 +4020,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Johan Råghall, Cecilia Goldkuhl, per-erik mukka, Christina Boyd, Moa Turid Lövdahl</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>96019446</v>
+        <v>135330905</v>
       </c>
       <c r="B35" t="n">
-        <v>91831</v>
+        <v>92027</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4042,37 +4043,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3242</v>
+        <v>2079</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Seitejaure, Pi lm</t>
+          <t>Maskaure Långmyran SV + Renskötartjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>617558</v>
+        <v>617574</v>
       </c>
       <c r="R35" t="n">
-        <v>7315745</v>
+        <v>7315632</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4096,12 +4097,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4116,19 +4127,23 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Julian Klein</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Julian Klein, Barbara Kühn, Björn Mildh, Kristina Bäck, Isak Vahlström, Maj Aspebo</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr"/>
+          <t>Elin Kannerby, Johan Råghall, Cecilia Goldkuhl, per-erik mukka, Christina Boyd, Moa Turid Lövdahl</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>96019447</v>
+        <v>96019446</v>
       </c>
       <c r="B36" t="n">
         <v>91831</v>
@@ -4163,10 +4178,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>617402</v>
+        <v>617558</v>
       </c>
       <c r="R36" t="n">
-        <v>7315828</v>
+        <v>7315745</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4225,10 +4240,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135325994</v>
+        <v>96019447</v>
       </c>
       <c r="B37" t="n">
-        <v>91896</v>
+        <v>91831</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4256,17 +4271,17 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Maskaure Renskötartjärnen, Pi lm</t>
+          <t>Seitejaure, Pi lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>617554</v>
+        <v>617402</v>
       </c>
       <c r="R37" t="n">
-        <v>7315710</v>
+        <v>7315828</v>
       </c>
       <c r="S37" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4290,22 +4305,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>15:19</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>15:19</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4320,64 +4325,60 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Julian Klein</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Julian Klein, Barbara Kühn, Björn Mildh, Kristina Bäck, Isak Vahlström, Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>96194518</v>
+        <v>135325994</v>
       </c>
       <c r="B38" t="n">
-        <v>93201</v>
+        <v>91896</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4365</v>
+        <v>3242</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Seitejaure, Pi lm</t>
+          <t>Maskaure Renskötartjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>617390</v>
+        <v>617554</v>
       </c>
       <c r="R38" t="n">
-        <v>7315768</v>
+        <v>7315710</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4401,12 +4402,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4421,44 +4432,48 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Barbara Kühn, Julian Klein, Björn Mildh, Kristina Bäck, Maj Aspebo</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr"/>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>96194501</v>
+        <v>96194518</v>
       </c>
       <c r="B39" t="n">
-        <v>93209</v>
+        <v>93201</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4366</v>
+        <v>4365</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4468,10 +4483,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>617535</v>
+        <v>617390</v>
       </c>
       <c r="R39" t="n">
-        <v>7315839</v>
+        <v>7315768</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4530,10 +4545,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>96194499</v>
+        <v>96194501</v>
       </c>
       <c r="B40" t="n">
-        <v>78730</v>
+        <v>93209</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4541,21 +4556,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6437</v>
+        <v>4366</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4565,10 +4580,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>617540</v>
+        <v>617535</v>
       </c>
       <c r="R40" t="n">
-        <v>7315810</v>
+        <v>7315839</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4627,7 +4642,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>96194529</v>
+        <v>96194499</v>
       </c>
       <c r="B41" t="n">
         <v>78730</v>
@@ -4662,10 +4677,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>617391</v>
+        <v>617540</v>
       </c>
       <c r="R41" t="n">
-        <v>7315876</v>
+        <v>7315810</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4724,7 +4739,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>96194530</v>
+        <v>96194529</v>
       </c>
       <c r="B42" t="n">
         <v>78730</v>
@@ -4759,10 +4774,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>617368</v>
+        <v>617391</v>
       </c>
       <c r="R42" t="n">
-        <v>7315854</v>
+        <v>7315876</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -4821,10 +4836,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135322914</v>
+        <v>96194530</v>
       </c>
       <c r="B43" t="n">
-        <v>78776</v>
+        <v>78730</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4852,17 +4867,17 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Renskötartjärnen, Pi lm</t>
+          <t>Seitejaure, Pi lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>617556</v>
+        <v>617368</v>
       </c>
       <c r="R43" t="n">
-        <v>7315832</v>
+        <v>7315854</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4886,22 +4901,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4916,23 +4921,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Isak Vahlström, Barbara Kühn, Julian Klein, Björn Mildh, Kristina Bäck, Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135322917</v>
+        <v>135322914</v>
       </c>
       <c r="B44" t="n">
         <v>78776</v>
@@ -4967,10 +4968,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>617543</v>
+        <v>617556</v>
       </c>
       <c r="R44" t="n">
-        <v>7315687</v>
+        <v>7315832</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5002,7 +5003,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5012,7 +5013,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5043,7 +5044,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135322921</v>
+        <v>135322917</v>
       </c>
       <c r="B45" t="n">
         <v>78776</v>
@@ -5078,10 +5079,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>617551</v>
+        <v>617543</v>
       </c>
       <c r="R45" t="n">
-        <v>7315614</v>
+        <v>7315687</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5113,7 +5114,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5123,7 +5124,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5154,7 +5155,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135322922</v>
+        <v>135322921</v>
       </c>
       <c r="B46" t="n">
         <v>78776</v>
@@ -5189,10 +5190,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>617446</v>
+        <v>617551</v>
       </c>
       <c r="R46" t="n">
-        <v>7315745</v>
+        <v>7315614</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5224,7 +5225,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5234,7 +5235,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5265,7 +5266,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135325988</v>
+        <v>135322922</v>
       </c>
       <c r="B47" t="n">
         <v>78776</v>
@@ -5296,14 +5297,14 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Maskaure Renskötartjärnen, Pi lm</t>
+          <t>Renskötartjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>617426</v>
+        <v>617446</v>
       </c>
       <c r="R47" t="n">
-        <v>7315822</v>
+        <v>7315745</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5335,7 +5336,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5345,7 +5346,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5360,12 +5361,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5376,7 +5377,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135325991</v>
+        <v>135325988</v>
       </c>
       <c r="B48" t="n">
         <v>78776</v>
@@ -5411,13 +5412,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>617467</v>
+        <v>617426</v>
       </c>
       <c r="R48" t="n">
-        <v>7315790</v>
+        <v>7315822</v>
       </c>
       <c r="S48" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5446,7 +5447,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5456,7 +5457,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5487,7 +5488,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135325995</v>
+        <v>135325991</v>
       </c>
       <c r="B49" t="n">
         <v>78776</v>
@@ -5522,13 +5523,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>617544</v>
+        <v>617467</v>
       </c>
       <c r="R49" t="n">
-        <v>7315719</v>
+        <v>7315790</v>
       </c>
       <c r="S49" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5557,7 +5558,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5567,7 +5568,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5598,7 +5599,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135325998</v>
+        <v>135325995</v>
       </c>
       <c r="B50" t="n">
         <v>78776</v>
@@ -5633,13 +5634,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>617566</v>
+        <v>617544</v>
       </c>
       <c r="R50" t="n">
-        <v>7315680</v>
+        <v>7315719</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5668,7 +5669,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5678,7 +5679,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5709,10 +5710,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>96019450</v>
+        <v>135325998</v>
       </c>
       <c r="B51" t="n">
-        <v>79946</v>
+        <v>78776</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5720,37 +5721,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Seitejaure, Pi lm</t>
+          <t>Maskaure Renskötartjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>617512</v>
+        <v>617566</v>
       </c>
       <c r="R51" t="n">
-        <v>7315786</v>
+        <v>7315680</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5774,12 +5775,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5794,22 +5805,26 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Julian Klein</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Julian Klein, Barbara Kühn, Björn Mildh, Kristina Bäck, Isak Vahlström, Maj Aspebo</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr"/>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135322912</v>
+        <v>96019450</v>
       </c>
       <c r="B52" t="n">
-        <v>79992</v>
+        <v>79946</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5837,17 +5852,17 @@
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Renskötartjärnen, Pi lm</t>
+          <t>Seitejaure, Pi lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>617490</v>
+        <v>617512</v>
       </c>
       <c r="R52" t="n">
-        <v>7315847</v>
+        <v>7315786</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5871,22 +5886,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>14:53</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>14:53</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5901,23 +5906,19 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Julian Klein</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
-        </is>
-      </c>
-      <c r="AY52" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Julian Klein, Barbara Kühn, Björn Mildh, Kristina Bäck, Isak Vahlström, Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135322919</v>
+        <v>135322912</v>
       </c>
       <c r="B53" t="n">
         <v>79992</v>
@@ -5952,10 +5953,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>617575</v>
+        <v>617490</v>
       </c>
       <c r="R53" t="n">
-        <v>7315656</v>
+        <v>7315847</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -5987,7 +5988,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -5997,7 +5998,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6028,7 +6029,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135322924</v>
+        <v>135322919</v>
       </c>
       <c r="B54" t="n">
         <v>79992</v>
@@ -6063,10 +6064,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>617370</v>
+        <v>617575</v>
       </c>
       <c r="R54" t="n">
-        <v>7315842</v>
+        <v>7315656</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6098,7 +6099,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6108,7 +6109,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6139,7 +6140,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>135323511</v>
+        <v>135322924</v>
       </c>
       <c r="B55" t="n">
         <v>79992</v>
@@ -6168,19 +6169,16 @@
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran SV + Renskötartjärnen_topo, Pi lm</t>
+          <t>Renskötartjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>617584</v>
+        <v>617370</v>
       </c>
       <c r="R55" t="n">
-        <v>7315763</v>
+        <v>7315842</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6212,7 +6210,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6222,7 +6220,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6231,19 +6229,18 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6254,7 +6251,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>135323515</v>
+        <v>135323511</v>
       </c>
       <c r="B56" t="n">
         <v>79992</v>
@@ -6283,16 +6280,19 @@
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Maskaure Långmyran SV + Renskötartjärnen_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>617465</v>
+        <v>617584</v>
       </c>
       <c r="R56" t="n">
-        <v>7315657</v>
+        <v>7315763</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6343,6 +6343,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6357,11 +6358,15 @@
           <t>Cecilia Goldkuhl</t>
         </is>
       </c>
-      <c r="AY56" t="inlineStr"/>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>135330907</v>
+        <v>135323515</v>
       </c>
       <c r="B57" t="n">
         <v>79992</v>
@@ -6392,17 +6397,17 @@
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran SV + Renskötartjärnen, Pi lm</t>
+          <t>Maskaure Långmyran SV + Renskötartjärnen_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>617555</v>
+        <v>617465</v>
       </c>
       <c r="R57" t="n">
-        <v>7315587</v>
+        <v>7315657</v>
       </c>
       <c r="S57" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6431,7 +6436,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6441,7 +6446,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6456,64 +6461,60 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Johan Råghall, Cecilia Goldkuhl, per-erik mukka, Christina Boyd, Moa Turid Lövdahl</t>
-        </is>
-      </c>
-      <c r="AY57" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>96019466</v>
+        <v>135330907</v>
       </c>
       <c r="B58" t="n">
-        <v>80468</v>
+        <v>79992</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6464</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Seitejaure, Pi lm</t>
+          <t>Maskaure Långmyran SV + Renskötartjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>617633</v>
+        <v>617555</v>
       </c>
       <c r="R58" t="n">
-        <v>7315774</v>
+        <v>7315587</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6537,12 +6538,22 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6557,60 +6568,64 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Julian Klein</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Julian Klein, Barbara Kühn, Björn Mildh, Kristina Bäck, Isak Vahlström, Maj Aspebo</t>
-        </is>
-      </c>
-      <c r="AY58" t="inlineStr"/>
+          <t>Elin Kannerby, Johan Råghall, Cecilia Goldkuhl, per-erik mukka, Christina Boyd, Moa Turid Lövdahl</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>135325987</v>
+        <v>96019466</v>
       </c>
       <c r="B59" t="n">
-        <v>78377</v>
+        <v>80468</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6487</v>
+        <v>6464</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Maskaure Renskötartjärnen, Pi lm</t>
+          <t>Seitejaure, Pi lm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>617425</v>
+        <v>617633</v>
       </c>
       <c r="R59" t="n">
-        <v>7315818</v>
+        <v>7315774</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6634,22 +6649,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>14:56</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>14:56</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6658,30 +6663,25 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Julian Klein</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
-        </is>
-      </c>
-      <c r="AY59" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Julian Klein, Barbara Kühn, Björn Mildh, Kristina Bäck, Isak Vahlström, Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>135325997</v>
+        <v>135325987</v>
       </c>
       <c r="B60" t="n">
         <v>78377</v>
@@ -6716,10 +6716,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>617566</v>
+        <v>617425</v>
       </c>
       <c r="R60" t="n">
-        <v>7315680</v>
+        <v>7315818</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6751,7 +6751,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6761,7 +6761,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6793,45 +6793,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>135329749</v>
+        <v>135325997</v>
       </c>
       <c r="B61" t="n">
-        <v>92661</v>
+        <v>78377</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>106596</v>
+        <v>6487</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Nordlig parasitporing</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Antrodiella pallasii</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Renvall &amp; al.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>_Maskaure Långmyran SV + Renskötartjärnen_topo, Pi lm</t>
+          <t>Maskaure Renskötartjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>617541</v>
+        <v>617566</v>
       </c>
       <c r="R61" t="n">
-        <v>7315552</v>
+        <v>7315680</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -6863,7 +6863,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -6873,12 +6873,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>15:48</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Ganska nedbruten granlåga</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6887,18 +6882,19 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Moa Turid Lövdahl</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Moa Turid Lövdahl</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -6909,45 +6905,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>135323517</v>
+        <v>135329749</v>
       </c>
       <c r="B62" t="n">
-        <v>98066</v>
+        <v>92661</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221941</v>
+        <v>106596</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Nordlig parasitporing</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Antrodiella pallasii</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Renvall &amp; al.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran SV + Renskötartjärnen_topo, Pi lm</t>
+          <t>_Maskaure Långmyran SV + Renskötartjärnen_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>617470</v>
+        <v>617541</v>
       </c>
       <c r="R62" t="n">
-        <v>7315735</v>
+        <v>7315552</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -6979,7 +6975,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -6989,7 +6985,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Ganska nedbruten granlåga</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7004,19 +7005,23 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Moa Turid Lövdahl</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
-        </is>
-      </c>
-      <c r="AY62" t="inlineStr"/>
+          <t>Moa Turid Lövdahl</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>135325993</v>
+        <v>135323517</v>
       </c>
       <c r="B63" t="n">
         <v>98066</v>
@@ -7047,14 +7052,14 @@
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Maskaure Renskötartjärnen, Pi lm</t>
+          <t>Maskaure Långmyran SV + Renskötartjärnen_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>617460</v>
+        <v>617470</v>
       </c>
       <c r="R63" t="n">
-        <v>7315781</v>
+        <v>7315735</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7086,7 +7091,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7096,7 +7101,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7111,67 +7116,60 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>135323508</v>
+        <v>135325993</v>
       </c>
       <c r="B64" t="n">
-        <v>79396</v>
+        <v>98066</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>260591</v>
+        <v>221941</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran SV + Renskötartjärnen_topo, Pi lm</t>
+          <t>Maskaure Renskötartjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>617490</v>
+        <v>617460</v>
       </c>
       <c r="R64" t="n">
-        <v>7315864</v>
+        <v>7315781</v>
       </c>
       <c r="S64" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7200,7 +7198,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7210,7 +7208,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7219,19 +7217,18 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -7242,7 +7239,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>135323510</v>
+        <v>135323508</v>
       </c>
       <c r="B65" t="n">
         <v>79396</v>
@@ -7280,13 +7277,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>617539</v>
+        <v>617490</v>
       </c>
       <c r="R65" t="n">
-        <v>7315769</v>
+        <v>7315864</v>
       </c>
       <c r="S65" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7315,7 +7312,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7325,7 +7322,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7357,27 +7354,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>135322920</v>
+        <v>135323510</v>
       </c>
       <c r="B66" t="n">
-        <v>80267</v>
+        <v>79396</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>266179</v>
+        <v>260591</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lecidea subhumida</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Vain.</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7386,17 +7388,17 @@
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Renskötartjärnen, Pi lm</t>
+          <t>Maskaure Långmyran SV + Renskötartjärnen_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>617594</v>
+        <v>617539</v>
       </c>
       <c r="R66" t="n">
-        <v>7315642</v>
+        <v>7315769</v>
       </c>
       <c r="S66" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7425,7 +7427,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7435,14 +7437,14 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
       <c r="AE66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
@@ -7451,12 +7453,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7467,32 +7469,27 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>96194519</v>
+        <v>135322920</v>
       </c>
       <c r="B67" t="n">
-        <v>92185</v>
+        <v>80267</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6008693</v>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Kritporing</t>
-        </is>
+        <v>266179</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Antrodia crassa</t>
+          <t>Lecidea subhumida</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>Vain.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7501,17 +7498,17 @@
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Seitejaure, Pi lm</t>
+          <t>Renskötartjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>617621</v>
+        <v>617594</v>
       </c>
       <c r="R67" t="n">
-        <v>7315742</v>
+        <v>7315642</v>
       </c>
       <c r="S67" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7535,19 +7532,29 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
@@ -7556,22 +7563,26 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Barbara Kühn, Julian Klein, Björn Mildh, Kristina Bäck, Maj Aspebo</t>
-        </is>
-      </c>
-      <c r="AY67" t="inlineStr"/>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>135323513</v>
+        <v>96194519</v>
       </c>
       <c r="B68" t="n">
-        <v>92222</v>
+        <v>92185</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7597,19 +7608,22 @@
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran SV + Renskötartjärnen_topo, Pi lm</t>
+          <t>Seitejaure, Pi lm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>617623</v>
+        <v>617621</v>
       </c>
       <c r="R68" t="n">
-        <v>7315761</v>
+        <v>7315742</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7633,22 +7647,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>15:14</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>15:14</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7661,75 +7665,60 @@
       <c r="AG68" t="b">
         <v>0</v>
       </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Isak Vahlström, Barbara Kühn, Julian Klein, Björn Mildh, Kristina Bäck, Maj Aspebo</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>135322908</v>
+        <v>135323513</v>
       </c>
       <c r="B69" t="n">
-        <v>79452</v>
+        <v>92222</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>864</v>
+        <v>6008693</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Kritporing</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Antrodia crassa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Renskötartjärnen, Pi lm</t>
+          <t>Maskaure Långmyran SV + Renskötartjärnen_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>617413</v>
+        <v>617623</v>
       </c>
       <c r="R69" t="n">
-        <v>7315903</v>
+        <v>7315761</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7761,7 +7750,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7771,7 +7760,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7780,6 +7769,7 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7801,26 +7791,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
-        </is>
-      </c>
-      <c r="AY69" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>135325985</v>
+        <v>135322908</v>
       </c>
       <c r="B70" t="n">
-        <v>81355</v>
+        <v>79452</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7828,31 +7814,31 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1049</v>
+        <v>864</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Maskaure Renskötartjärnen, Pi lm</t>
+          <t>Renskötartjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>617385</v>
+        <v>617413</v>
       </c>
       <c r="R70" t="n">
         <v>7315903</v>
@@ -7887,7 +7873,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -7897,7 +7883,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7906,19 +7892,33 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -7929,10 +7929,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>135325981</v>
+        <v>135325985</v>
       </c>
       <c r="B71" t="n">
-        <v>92027</v>
+        <v>81355</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7940,21 +7940,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2079</v>
+        <v>1049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7964,13 +7964,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>617398</v>
+        <v>617385</v>
       </c>
       <c r="R71" t="n">
-        <v>7315912</v>
+        <v>7315903</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7999,7 +7999,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8009,7 +8009,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8018,6 +8018,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8040,10 +8041,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>135322907</v>
+        <v>135325981</v>
       </c>
       <c r="B72" t="n">
-        <v>78776</v>
+        <v>92027</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8051,37 +8052,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6437</v>
+        <v>2079</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Renskötartjärnen, Pi lm</t>
+          <t>Maskaure Renskötartjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>617410</v>
+        <v>617398</v>
       </c>
       <c r="R72" t="n">
-        <v>7315918</v>
+        <v>7315912</v>
       </c>
       <c r="S72" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8110,7 +8111,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8120,7 +8121,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8135,12 +8136,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -8151,7 +8152,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>135325984</v>
+        <v>135322907</v>
       </c>
       <c r="B73" t="n">
         <v>78776</v>
@@ -8182,17 +8183,17 @@
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Maskaure Renskötartjärnen, Pi lm</t>
+          <t>Renskötartjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>617385</v>
+        <v>617410</v>
       </c>
       <c r="R73" t="n">
-        <v>7315903</v>
+        <v>7315918</v>
       </c>
       <c r="S73" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8221,7 +8222,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8231,7 +8232,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8246,12 +8247,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -8262,7 +8263,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>135326431</v>
+        <v>135325984</v>
       </c>
       <c r="B74" t="n">
         <v>78776</v>
@@ -8293,17 +8294,17 @@
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_topo, Pi lm</t>
+          <t>Maskaure Renskötartjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>617403</v>
+        <v>617385</v>
       </c>
       <c r="R74" t="n">
-        <v>7315880</v>
+        <v>7315903</v>
       </c>
       <c r="S74" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8332,7 +8333,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8342,7 +8343,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8357,12 +8358,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -8373,10 +8374,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>135322909</v>
+        <v>135326431</v>
       </c>
       <c r="B75" t="n">
-        <v>79992</v>
+        <v>78776</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8384,37 +8385,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Renskötartjärnen, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>617413</v>
+        <v>617403</v>
       </c>
       <c r="R75" t="n">
-        <v>7315903</v>
+        <v>7315880</v>
       </c>
       <c r="S75" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8443,7 +8444,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8453,7 +8454,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8468,12 +8469,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -8484,7 +8485,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>135329744</v>
+        <v>135322909</v>
       </c>
       <c r="B76" t="n">
         <v>79992</v>
@@ -8515,14 +8516,14 @@
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>_Maskaure Långmyran SV + Renskötartjärnen_topo, Pi lm</t>
+          <t>Renskötartjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>617411</v>
+        <v>617413</v>
       </c>
       <c r="R76" t="n">
-        <v>7315912</v>
+        <v>7315903</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8579,12 +8580,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Moa Turid Lövdahl</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Moa Turid Lövdahl</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -8595,7 +8596,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>135330899</v>
+        <v>135329744</v>
       </c>
       <c r="B77" t="n">
         <v>79992</v>
@@ -8626,17 +8627,17 @@
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran SV + Renskötartjärnen, Pi lm</t>
+          <t>_Maskaure Långmyran SV + Renskötartjärnen_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>617384</v>
+        <v>617411</v>
       </c>
       <c r="R77" t="n">
-        <v>7315902</v>
+        <v>7315912</v>
       </c>
       <c r="S77" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8665,7 +8666,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8675,7 +8676,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8690,12 +8691,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Moa Turid Lövdahl</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Johan Råghall, Cecilia Goldkuhl, per-erik mukka, Christina Boyd, Moa Turid Lövdahl</t>
+          <t>Moa Turid Lövdahl</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -8706,10 +8707,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>135325986</v>
+        <v>135330899</v>
       </c>
       <c r="B78" t="n">
-        <v>78377</v>
+        <v>79992</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8717,37 +8718,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Maskaure Renskötartjärnen, Pi lm</t>
+          <t>Maskaure Långmyran SV + Renskötartjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>617385</v>
+        <v>617384</v>
       </c>
       <c r="R78" t="n">
-        <v>7315903</v>
+        <v>7315902</v>
       </c>
       <c r="S78" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8776,7 +8777,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8786,7 +8787,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8795,19 +8796,18 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Elin Kannerby, Johan Råghall, Cecilia Goldkuhl, per-erik mukka, Christina Boyd, Moa Turid Lövdahl</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -8818,10 +8818,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>135326430</v>
+        <v>135325986</v>
       </c>
       <c r="B79" t="n">
-        <v>79131</v>
+        <v>78377</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8829,37 +8829,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_topo, Pi lm</t>
+          <t>Maskaure Renskötartjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>617403</v>
+        <v>617385</v>
       </c>
       <c r="R79" t="n">
-        <v>7315880</v>
+        <v>7315903</v>
       </c>
       <c r="S79" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8888,7 +8888,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -8898,7 +8898,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8907,18 +8907,19 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -8929,10 +8930,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>135323518</v>
+        <v>135326430</v>
       </c>
       <c r="B80" t="n">
-        <v>79396</v>
+        <v>79131</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8940,37 +8941,37 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>260591</v>
+        <v>228912</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran SV + Renskötartjärnen_topo, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>617376</v>
+        <v>617403</v>
       </c>
       <c r="R80" t="n">
-        <v>7315923</v>
+        <v>7315880</v>
       </c>
       <c r="S80" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8999,7 +9000,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9009,7 +9010,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9024,15 +9025,126 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>135323518</v>
+      </c>
+      <c r="B81" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Maskaure Långmyran SV + Renskötartjärnen_topo, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>617376</v>
+      </c>
+      <c r="R81" t="n">
+        <v>7315923</v>
+      </c>
+      <c r="S81" t="n">
+        <v>5</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
           <t>Cecilia Goldkuhl</t>
         </is>
       </c>
-      <c r="AX80" t="inlineStr">
+      <c r="AX81" t="inlineStr">
         <is>
           <t>Cecilia Goldkuhl</t>
         </is>
       </c>
-      <c r="AY80" t="inlineStr"/>
+      <c r="AY81" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/Maskaure Renskötartjärnen, 8,3 ha artfynd.xlsx
+++ b/artfynd/Maskaure Renskötartjärnen, 8,3 ha artfynd.xlsx
@@ -7010,7 +7010,7 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Moa Turid Lövdahl</t>
+          <t>Moa Turid Lövdahl, per-erik mukka</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -7796,7 +7796,7 @@
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, per-erik mukka</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>

--- a/artfynd/Maskaure Renskötartjärnen, 8,3 ha artfynd.xlsx
+++ b/artfynd/Maskaure Renskötartjärnen, 8,3 ha artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY81"/>
+  <dimension ref="A1:AY82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4143,48 +4143,52 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>96019446</v>
+        <v>135325992</v>
       </c>
       <c r="B36" t="n">
-        <v>91831</v>
+        <v>97308</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3242</v>
+        <v>2869</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Seitejaure, Pi lm</t>
+          <t>Maskaure Renskötartjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>617558</v>
+        <v>617462</v>
       </c>
       <c r="R36" t="n">
-        <v>7315745</v>
+        <v>7315746</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4208,12 +4212,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4222,25 +4236,30 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Julian Klein</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Julian Klein, Barbara Kühn, Björn Mildh, Kristina Bäck, Isak Vahlström, Maj Aspebo</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr"/>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>96019447</v>
+        <v>96019446</v>
       </c>
       <c r="B37" t="n">
         <v>91831</v>
@@ -4275,10 +4294,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>617402</v>
+        <v>617558</v>
       </c>
       <c r="R37" t="n">
-        <v>7315828</v>
+        <v>7315745</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4337,10 +4356,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135325994</v>
+        <v>96019447</v>
       </c>
       <c r="B38" t="n">
-        <v>91896</v>
+        <v>91831</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4368,17 +4387,17 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Maskaure Renskötartjärnen, Pi lm</t>
+          <t>Seitejaure, Pi lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>617554</v>
+        <v>617402</v>
       </c>
       <c r="R38" t="n">
-        <v>7315710</v>
+        <v>7315828</v>
       </c>
       <c r="S38" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4402,22 +4421,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>15:19</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>15:19</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4432,64 +4441,60 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Julian Klein</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Julian Klein, Barbara Kühn, Björn Mildh, Kristina Bäck, Isak Vahlström, Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>96194518</v>
+        <v>135325994</v>
       </c>
       <c r="B39" t="n">
-        <v>93201</v>
+        <v>91896</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4365</v>
+        <v>3242</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Seitejaure, Pi lm</t>
+          <t>Maskaure Renskötartjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>617390</v>
+        <v>617554</v>
       </c>
       <c r="R39" t="n">
-        <v>7315768</v>
+        <v>7315710</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4513,12 +4518,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4533,44 +4548,48 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Barbara Kühn, Julian Klein, Björn Mildh, Kristina Bäck, Maj Aspebo</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr"/>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>96194501</v>
+        <v>96194518</v>
       </c>
       <c r="B40" t="n">
-        <v>93209</v>
+        <v>93201</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4366</v>
+        <v>4365</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4580,10 +4599,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>617535</v>
+        <v>617390</v>
       </c>
       <c r="R40" t="n">
-        <v>7315839</v>
+        <v>7315768</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4642,10 +4661,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>96194499</v>
+        <v>96194501</v>
       </c>
       <c r="B41" t="n">
-        <v>78730</v>
+        <v>93209</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4653,21 +4672,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6437</v>
+        <v>4366</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4677,10 +4696,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>617540</v>
+        <v>617535</v>
       </c>
       <c r="R41" t="n">
-        <v>7315810</v>
+        <v>7315839</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4739,7 +4758,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>96194529</v>
+        <v>96194499</v>
       </c>
       <c r="B42" t="n">
         <v>78730</v>
@@ -4774,10 +4793,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>617391</v>
+        <v>617540</v>
       </c>
       <c r="R42" t="n">
-        <v>7315876</v>
+        <v>7315810</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -4836,7 +4855,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>96194530</v>
+        <v>96194529</v>
       </c>
       <c r="B43" t="n">
         <v>78730</v>
@@ -4871,10 +4890,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>617368</v>
+        <v>617391</v>
       </c>
       <c r="R43" t="n">
-        <v>7315854</v>
+        <v>7315876</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -4933,10 +4952,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135322914</v>
+        <v>96194530</v>
       </c>
       <c r="B44" t="n">
-        <v>78776</v>
+        <v>78730</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4964,17 +4983,17 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Renskötartjärnen, Pi lm</t>
+          <t>Seitejaure, Pi lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>617556</v>
+        <v>617368</v>
       </c>
       <c r="R44" t="n">
-        <v>7315832</v>
+        <v>7315854</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4998,22 +5017,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5028,23 +5037,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Isak Vahlström, Barbara Kühn, Julian Klein, Björn Mildh, Kristina Bäck, Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135322917</v>
+        <v>135322914</v>
       </c>
       <c r="B45" t="n">
         <v>78776</v>
@@ -5079,10 +5084,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>617543</v>
+        <v>617556</v>
       </c>
       <c r="R45" t="n">
-        <v>7315687</v>
+        <v>7315832</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5114,7 +5119,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5124,7 +5129,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5155,7 +5160,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135322921</v>
+        <v>135322917</v>
       </c>
       <c r="B46" t="n">
         <v>78776</v>
@@ -5190,10 +5195,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>617551</v>
+        <v>617543</v>
       </c>
       <c r="R46" t="n">
-        <v>7315614</v>
+        <v>7315687</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5225,7 +5230,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5235,7 +5240,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5266,7 +5271,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135322922</v>
+        <v>135322921</v>
       </c>
       <c r="B47" t="n">
         <v>78776</v>
@@ -5301,10 +5306,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>617446</v>
+        <v>617551</v>
       </c>
       <c r="R47" t="n">
-        <v>7315745</v>
+        <v>7315614</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5336,7 +5341,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5346,7 +5351,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5377,7 +5382,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135325988</v>
+        <v>135322922</v>
       </c>
       <c r="B48" t="n">
         <v>78776</v>
@@ -5408,14 +5413,14 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Maskaure Renskötartjärnen, Pi lm</t>
+          <t>Renskötartjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>617426</v>
+        <v>617446</v>
       </c>
       <c r="R48" t="n">
-        <v>7315822</v>
+        <v>7315745</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5447,7 +5452,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5457,7 +5462,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5472,12 +5477,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5488,7 +5493,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135325991</v>
+        <v>135325988</v>
       </c>
       <c r="B49" t="n">
         <v>78776</v>
@@ -5523,13 +5528,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>617467</v>
+        <v>617426</v>
       </c>
       <c r="R49" t="n">
-        <v>7315790</v>
+        <v>7315822</v>
       </c>
       <c r="S49" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5558,7 +5563,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5568,7 +5573,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5599,7 +5604,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135325995</v>
+        <v>135325991</v>
       </c>
       <c r="B50" t="n">
         <v>78776</v>
@@ -5634,13 +5639,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>617544</v>
+        <v>617467</v>
       </c>
       <c r="R50" t="n">
-        <v>7315719</v>
+        <v>7315790</v>
       </c>
       <c r="S50" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5669,7 +5674,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5679,7 +5684,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5710,7 +5715,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135325998</v>
+        <v>135325995</v>
       </c>
       <c r="B51" t="n">
         <v>78776</v>
@@ -5745,13 +5750,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>617566</v>
+        <v>617544</v>
       </c>
       <c r="R51" t="n">
-        <v>7315680</v>
+        <v>7315719</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5780,7 +5785,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5790,7 +5795,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5821,10 +5826,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>96019450</v>
+        <v>135325998</v>
       </c>
       <c r="B52" t="n">
-        <v>79946</v>
+        <v>78776</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5832,37 +5837,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Seitejaure, Pi lm</t>
+          <t>Maskaure Renskötartjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>617512</v>
+        <v>617566</v>
       </c>
       <c r="R52" t="n">
-        <v>7315786</v>
+        <v>7315680</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5886,12 +5891,22 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5906,22 +5921,26 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Julian Klein</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Julian Klein, Barbara Kühn, Björn Mildh, Kristina Bäck, Isak Vahlström, Maj Aspebo</t>
-        </is>
-      </c>
-      <c r="AY52" t="inlineStr"/>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135322912</v>
+        <v>96019450</v>
       </c>
       <c r="B53" t="n">
-        <v>79992</v>
+        <v>79946</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5949,17 +5968,17 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Renskötartjärnen, Pi lm</t>
+          <t>Seitejaure, Pi lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>617490</v>
+        <v>617512</v>
       </c>
       <c r="R53" t="n">
-        <v>7315847</v>
+        <v>7315786</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5983,22 +6002,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>14:53</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>14:53</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6013,23 +6022,19 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Julian Klein</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
-        </is>
-      </c>
-      <c r="AY53" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Julian Klein, Barbara Kühn, Björn Mildh, Kristina Bäck, Isak Vahlström, Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135322919</v>
+        <v>135322912</v>
       </c>
       <c r="B54" t="n">
         <v>79992</v>
@@ -6064,10 +6069,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>617575</v>
+        <v>617490</v>
       </c>
       <c r="R54" t="n">
-        <v>7315656</v>
+        <v>7315847</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6099,7 +6104,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6109,7 +6114,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6140,7 +6145,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>135322924</v>
+        <v>135322919</v>
       </c>
       <c r="B55" t="n">
         <v>79992</v>
@@ -6175,10 +6180,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>617370</v>
+        <v>617575</v>
       </c>
       <c r="R55" t="n">
-        <v>7315842</v>
+        <v>7315656</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6210,7 +6215,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6220,7 +6225,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6251,7 +6256,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>135323511</v>
+        <v>135322924</v>
       </c>
       <c r="B56" t="n">
         <v>79992</v>
@@ -6280,19 +6285,16 @@
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran SV + Renskötartjärnen_topo, Pi lm</t>
+          <t>Renskötartjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>617584</v>
+        <v>617370</v>
       </c>
       <c r="R56" t="n">
-        <v>7315763</v>
+        <v>7315842</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6324,7 +6326,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6334,7 +6336,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6343,19 +6345,18 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6366,7 +6367,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>135323515</v>
+        <v>135323511</v>
       </c>
       <c r="B57" t="n">
         <v>79992</v>
@@ -6395,16 +6396,19 @@
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Maskaure Långmyran SV + Renskötartjärnen_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>617465</v>
+        <v>617584</v>
       </c>
       <c r="R57" t="n">
-        <v>7315657</v>
+        <v>7315763</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6436,7 +6440,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6446,7 +6450,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6455,6 +6459,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6469,11 +6474,15 @@
           <t>Cecilia Goldkuhl</t>
         </is>
       </c>
-      <c r="AY57" t="inlineStr"/>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>135330907</v>
+        <v>135323515</v>
       </c>
       <c r="B58" t="n">
         <v>79992</v>
@@ -6504,17 +6513,17 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran SV + Renskötartjärnen, Pi lm</t>
+          <t>Maskaure Långmyran SV + Renskötartjärnen_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>617555</v>
+        <v>617465</v>
       </c>
       <c r="R58" t="n">
-        <v>7315587</v>
+        <v>7315657</v>
       </c>
       <c r="S58" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6543,7 +6552,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6553,7 +6562,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6568,64 +6577,60 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Johan Råghall, Cecilia Goldkuhl, per-erik mukka, Christina Boyd, Moa Turid Lövdahl</t>
-        </is>
-      </c>
-      <c r="AY58" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>96019466</v>
+        <v>135330907</v>
       </c>
       <c r="B59" t="n">
-        <v>80468</v>
+        <v>79992</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6464</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Seitejaure, Pi lm</t>
+          <t>Maskaure Långmyran SV + Renskötartjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>617633</v>
+        <v>617555</v>
       </c>
       <c r="R59" t="n">
-        <v>7315774</v>
+        <v>7315587</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6649,12 +6654,22 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6669,60 +6684,64 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Julian Klein</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Julian Klein, Barbara Kühn, Björn Mildh, Kristina Bäck, Isak Vahlström, Maj Aspebo</t>
-        </is>
-      </c>
-      <c r="AY59" t="inlineStr"/>
+          <t>Elin Kannerby, Johan Råghall, Cecilia Goldkuhl, per-erik mukka, Christina Boyd, Moa Turid Lövdahl</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>135325987</v>
+        <v>96019466</v>
       </c>
       <c r="B60" t="n">
-        <v>78377</v>
+        <v>80468</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6487</v>
+        <v>6464</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Maskaure Renskötartjärnen, Pi lm</t>
+          <t>Seitejaure, Pi lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>617425</v>
+        <v>617633</v>
       </c>
       <c r="R60" t="n">
-        <v>7315818</v>
+        <v>7315774</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6746,22 +6765,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>14:56</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>14:56</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6770,30 +6779,25 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Julian Klein</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
-        </is>
-      </c>
-      <c r="AY60" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Julian Klein, Barbara Kühn, Björn Mildh, Kristina Bäck, Isak Vahlström, Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>135325997</v>
+        <v>135325987</v>
       </c>
       <c r="B61" t="n">
         <v>78377</v>
@@ -6828,10 +6832,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>617566</v>
+        <v>617425</v>
       </c>
       <c r="R61" t="n">
-        <v>7315680</v>
+        <v>7315818</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -6863,7 +6867,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -6873,7 +6877,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6905,45 +6909,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>135329749</v>
+        <v>135325997</v>
       </c>
       <c r="B62" t="n">
-        <v>92661</v>
+        <v>78377</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>106596</v>
+        <v>6487</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Nordlig parasitporing</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Antrodiella pallasii</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Renvall &amp; al.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>_Maskaure Långmyran SV + Renskötartjärnen_topo, Pi lm</t>
+          <t>Maskaure Renskötartjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>617541</v>
+        <v>617566</v>
       </c>
       <c r="R62" t="n">
-        <v>7315552</v>
+        <v>7315680</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -6975,7 +6979,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -6985,12 +6989,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:48</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Ganska nedbruten granlåga</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6999,18 +6998,19 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Moa Turid Lövdahl</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Moa Turid Lövdahl, per-erik mukka</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -7021,45 +7021,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>135323517</v>
+        <v>135329749</v>
       </c>
       <c r="B63" t="n">
-        <v>98066</v>
+        <v>92661</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>221941</v>
+        <v>106596</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Nordlig parasitporing</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Antrodiella pallasii</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Renvall &amp; al.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran SV + Renskötartjärnen_topo, Pi lm</t>
+          <t>_Maskaure Långmyran SV + Renskötartjärnen_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>617470</v>
+        <v>617541</v>
       </c>
       <c r="R63" t="n">
-        <v>7315735</v>
+        <v>7315552</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7091,7 +7091,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7101,7 +7101,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ganska nedbruten granlåga</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7116,19 +7121,23 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Moa Turid Lövdahl</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr"/>
+          <t>Moa Turid Lövdahl, per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>135325993</v>
+        <v>135323517</v>
       </c>
       <c r="B64" t="n">
         <v>98066</v>
@@ -7159,14 +7168,14 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Maskaure Renskötartjärnen, Pi lm</t>
+          <t>Maskaure Långmyran SV + Renskötartjärnen_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>617460</v>
+        <v>617470</v>
       </c>
       <c r="R64" t="n">
-        <v>7315781</v>
+        <v>7315735</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7198,7 +7207,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7208,7 +7217,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7223,67 +7232,60 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
-        </is>
-      </c>
-      <c r="AY64" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>135323508</v>
+        <v>135325993</v>
       </c>
       <c r="B65" t="n">
-        <v>79396</v>
+        <v>98066</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>260591</v>
+        <v>221941</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran SV + Renskötartjärnen_topo, Pi lm</t>
+          <t>Maskaure Renskötartjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>617490</v>
+        <v>617460</v>
       </c>
       <c r="R65" t="n">
-        <v>7315864</v>
+        <v>7315781</v>
       </c>
       <c r="S65" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7312,7 +7314,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7322,7 +7324,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7331,19 +7333,18 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7354,7 +7355,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>135323510</v>
+        <v>135323508</v>
       </c>
       <c r="B66" t="n">
         <v>79396</v>
@@ -7392,13 +7393,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>617539</v>
+        <v>617490</v>
       </c>
       <c r="R66" t="n">
-        <v>7315769</v>
+        <v>7315864</v>
       </c>
       <c r="S66" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7427,7 +7428,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7437,7 +7438,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7469,27 +7470,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>135322920</v>
+        <v>135323510</v>
       </c>
       <c r="B67" t="n">
-        <v>80267</v>
+        <v>79396</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>266179</v>
+        <v>260591</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lecidea subhumida</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Vain.</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7498,17 +7504,17 @@
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Renskötartjärnen, Pi lm</t>
+          <t>Maskaure Långmyran SV + Renskötartjärnen_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>617594</v>
+        <v>617539</v>
       </c>
       <c r="R67" t="n">
-        <v>7315642</v>
+        <v>7315769</v>
       </c>
       <c r="S67" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7537,7 +7543,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7547,14 +7553,14 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
@@ -7563,12 +7569,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7579,32 +7585,27 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>96194519</v>
+        <v>135322920</v>
       </c>
       <c r="B68" t="n">
-        <v>92185</v>
+        <v>80267</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6008693</v>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Kritporing</t>
-        </is>
+        <v>266179</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Antrodia crassa</t>
+          <t>Lecidea subhumida</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>Vain.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7613,17 +7614,17 @@
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Seitejaure, Pi lm</t>
+          <t>Renskötartjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>617621</v>
+        <v>617594</v>
       </c>
       <c r="R68" t="n">
-        <v>7315742</v>
+        <v>7315642</v>
       </c>
       <c r="S68" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7647,19 +7648,29 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
@@ -7668,22 +7679,26 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Barbara Kühn, Julian Klein, Björn Mildh, Kristina Bäck, Maj Aspebo</t>
-        </is>
-      </c>
-      <c r="AY68" t="inlineStr"/>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>135323513</v>
+        <v>96194519</v>
       </c>
       <c r="B69" t="n">
-        <v>92222</v>
+        <v>92185</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7709,19 +7724,22 @@
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran SV + Renskötartjärnen_topo, Pi lm</t>
+          <t>Seitejaure, Pi lm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>617623</v>
+        <v>617621</v>
       </c>
       <c r="R69" t="n">
-        <v>7315761</v>
+        <v>7315742</v>
       </c>
       <c r="S69" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7745,22 +7763,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>15:14</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>15:14</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7773,75 +7781,60 @@
       <c r="AG69" t="b">
         <v>0</v>
       </c>
-      <c r="AJ69" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK69" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO69" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, per-erik mukka</t>
+          <t>Isak Vahlström, Barbara Kühn, Julian Klein, Björn Mildh, Kristina Bäck, Maj Aspebo</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>135322908</v>
+        <v>135323513</v>
       </c>
       <c r="B70" t="n">
-        <v>79452</v>
+        <v>92222</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>864</v>
+        <v>6008693</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Kritporing</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Antrodia crassa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Renskötartjärnen, Pi lm</t>
+          <t>Maskaure Långmyran SV + Renskötartjärnen_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>617413</v>
+        <v>617623</v>
       </c>
       <c r="R70" t="n">
-        <v>7315903</v>
+        <v>7315761</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -7873,7 +7866,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -7883,7 +7876,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7892,6 +7885,7 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7913,26 +7907,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
-        </is>
-      </c>
-      <c r="AY70" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Cecilia Goldkuhl, per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>135325985</v>
+        <v>135322908</v>
       </c>
       <c r="B71" t="n">
-        <v>81355</v>
+        <v>79452</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7940,31 +7930,31 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1049</v>
+        <v>864</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Maskaure Renskötartjärnen, Pi lm</t>
+          <t>Renskötartjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>617385</v>
+        <v>617413</v>
       </c>
       <c r="R71" t="n">
         <v>7315903</v>
@@ -7999,7 +7989,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8009,7 +7999,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8018,19 +8008,33 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -8041,10 +8045,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>135325981</v>
+        <v>135325985</v>
       </c>
       <c r="B72" t="n">
-        <v>92027</v>
+        <v>81355</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8052,21 +8056,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2079</v>
+        <v>1049</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8076,13 +8080,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>617398</v>
+        <v>617385</v>
       </c>
       <c r="R72" t="n">
-        <v>7315912</v>
+        <v>7315903</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8111,7 +8115,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8121,7 +8125,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8130,6 +8134,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8152,10 +8157,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>135322907</v>
+        <v>135325981</v>
       </c>
       <c r="B73" t="n">
-        <v>78776</v>
+        <v>92027</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8163,37 +8168,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6437</v>
+        <v>2079</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Renskötartjärnen, Pi lm</t>
+          <t>Maskaure Renskötartjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>617410</v>
+        <v>617398</v>
       </c>
       <c r="R73" t="n">
-        <v>7315918</v>
+        <v>7315912</v>
       </c>
       <c r="S73" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8222,7 +8227,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8232,7 +8237,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8247,12 +8252,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -8263,7 +8268,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>135325984</v>
+        <v>135322907</v>
       </c>
       <c r="B74" t="n">
         <v>78776</v>
@@ -8294,17 +8299,17 @@
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Maskaure Renskötartjärnen, Pi lm</t>
+          <t>Renskötartjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>617385</v>
+        <v>617410</v>
       </c>
       <c r="R74" t="n">
-        <v>7315903</v>
+        <v>7315918</v>
       </c>
       <c r="S74" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8333,7 +8338,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8343,7 +8348,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8358,12 +8363,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -8374,7 +8379,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>135326431</v>
+        <v>135325984</v>
       </c>
       <c r="B75" t="n">
         <v>78776</v>
@@ -8405,17 +8410,17 @@
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_topo, Pi lm</t>
+          <t>Maskaure Renskötartjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>617403</v>
+        <v>617385</v>
       </c>
       <c r="R75" t="n">
-        <v>7315880</v>
+        <v>7315903</v>
       </c>
       <c r="S75" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8444,7 +8449,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8454,7 +8459,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8469,12 +8474,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -8485,10 +8490,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>135322909</v>
+        <v>135326431</v>
       </c>
       <c r="B76" t="n">
-        <v>79992</v>
+        <v>78776</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8496,37 +8501,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Renskötartjärnen, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>617413</v>
+        <v>617403</v>
       </c>
       <c r="R76" t="n">
-        <v>7315903</v>
+        <v>7315880</v>
       </c>
       <c r="S76" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8555,7 +8560,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8565,7 +8570,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8580,12 +8585,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -8596,7 +8601,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>135329744</v>
+        <v>135322909</v>
       </c>
       <c r="B77" t="n">
         <v>79992</v>
@@ -8627,14 +8632,14 @@
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>_Maskaure Långmyran SV + Renskötartjärnen_topo, Pi lm</t>
+          <t>Renskötartjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>617411</v>
+        <v>617413</v>
       </c>
       <c r="R77" t="n">
-        <v>7315912</v>
+        <v>7315903</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8691,12 +8696,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Moa Turid Lövdahl</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Moa Turid Lövdahl</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -8707,7 +8712,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>135330899</v>
+        <v>135329744</v>
       </c>
       <c r="B78" t="n">
         <v>79992</v>
@@ -8738,17 +8743,17 @@
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran SV + Renskötartjärnen, Pi lm</t>
+          <t>_Maskaure Långmyran SV + Renskötartjärnen_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>617384</v>
+        <v>617411</v>
       </c>
       <c r="R78" t="n">
-        <v>7315902</v>
+        <v>7315912</v>
       </c>
       <c r="S78" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8777,7 +8782,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8787,7 +8792,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8802,12 +8807,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Moa Turid Lövdahl</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Johan Råghall, Cecilia Goldkuhl, per-erik mukka, Christina Boyd, Moa Turid Lövdahl</t>
+          <t>Moa Turid Lövdahl</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -8818,10 +8823,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>135325986</v>
+        <v>135330899</v>
       </c>
       <c r="B79" t="n">
-        <v>78377</v>
+        <v>79992</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8829,37 +8834,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Maskaure Renskötartjärnen, Pi lm</t>
+          <t>Maskaure Långmyran SV + Renskötartjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>617385</v>
+        <v>617384</v>
       </c>
       <c r="R79" t="n">
-        <v>7315903</v>
+        <v>7315902</v>
       </c>
       <c r="S79" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8888,7 +8893,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -8898,7 +8903,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8907,19 +8912,18 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Elin Kannerby, Johan Råghall, Cecilia Goldkuhl, per-erik mukka, Christina Boyd, Moa Turid Lövdahl</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -8930,10 +8934,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>135326430</v>
+        <v>135325986</v>
       </c>
       <c r="B80" t="n">
-        <v>79131</v>
+        <v>78377</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8941,37 +8945,37 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_topo, Pi lm</t>
+          <t>Maskaure Renskötartjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>617403</v>
+        <v>617385</v>
       </c>
       <c r="R80" t="n">
-        <v>7315880</v>
+        <v>7315903</v>
       </c>
       <c r="S80" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9000,7 +9004,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9010,7 +9014,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9019,18 +9023,19 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -9041,10 +9046,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>135323518</v>
+        <v>135326430</v>
       </c>
       <c r="B81" t="n">
-        <v>79396</v>
+        <v>79131</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9052,37 +9057,37 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>260591</v>
+        <v>228912</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Maskaure Långmyran SV + Renskötartjärnen_topo, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>617376</v>
+        <v>617403</v>
       </c>
       <c r="R81" t="n">
-        <v>7315923</v>
+        <v>7315880</v>
       </c>
       <c r="S81" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9111,7 +9116,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9121,7 +9126,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9136,15 +9141,126 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>135323518</v>
+      </c>
+      <c r="B82" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Maskaure Långmyran SV + Renskötartjärnen_topo, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>617376</v>
+      </c>
+      <c r="R82" t="n">
+        <v>7315923</v>
+      </c>
+      <c r="S82" t="n">
+        <v>5</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
           <t>Cecilia Goldkuhl</t>
         </is>
       </c>
-      <c r="AX81" t="inlineStr">
+      <c r="AX82" t="inlineStr">
         <is>
           <t>Cecilia Goldkuhl</t>
         </is>
       </c>
-      <c r="AY81" t="inlineStr"/>
+      <c r="AY82" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/Maskaure Renskötartjärnen, 8,3 ha artfynd.xlsx
+++ b/artfynd/Maskaure Renskötartjärnen, 8,3 ha artfynd.xlsx
@@ -7126,7 +7126,7 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Moa Turid Lövdahl, per-erik mukka</t>
+          <t>Moa Turid Lövdahl, per-erik mukka, Johan Råghall</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">

--- a/artfynd/Maskaure Renskötartjärnen, 8,3 ha artfynd.xlsx
+++ b/artfynd/Maskaure Renskötartjärnen, 8,3 ha artfynd.xlsx
@@ -7126,7 +7126,7 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Moa Turid Lövdahl, per-erik mukka, Johan Råghall</t>
+          <t>Moa Turid Lövdahl, Johan Råghall, per-erik mukka</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">

--- a/artfynd/Maskaure Renskötartjärnen, 8,3 ha artfynd.xlsx
+++ b/artfynd/Maskaure Renskötartjärnen, 8,3 ha artfynd.xlsx
@@ -7126,7 +7126,7 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Moa Turid Lövdahl, Johan Råghall, per-erik mukka</t>
+          <t>Moa Turid Lövdahl, per-erik mukka, Johan Råghall</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">

--- a/artfynd/Maskaure Renskötartjärnen, 8,3 ha artfynd.xlsx
+++ b/artfynd/Maskaure Renskötartjärnen, 8,3 ha artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY82"/>
+  <dimension ref="A1:AZ82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135322925</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96194513</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -977,6 +992,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96194533</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1074,6 +1094,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96194532</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1171,6 +1196,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96194512</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1268,6 +1298,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96194523</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1365,6 +1400,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96019461</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1462,6 +1502,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96194537</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1559,6 +1604,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96194520</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1656,6 +1706,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96194525</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1753,6 +1808,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96019452</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1850,6 +1910,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96194522</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1947,6 +2012,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96194534</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2044,6 +2114,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96194524</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2141,6 +2216,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96019494</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2252,6 +2332,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135322916</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2364,6 +2449,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326001</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2461,6 +2551,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96019500</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2558,6 +2653,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96194508</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2669,6 +2769,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135322911</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2778,6 +2883,11 @@
       <c r="AY22" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135322923</t>
         </is>
       </c>
     </row>
@@ -2895,6 +3005,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323509</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3002,6 +3117,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323514</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3113,6 +3233,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330900</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3210,6 +3335,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96194504</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3307,6 +3437,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96019487</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3404,6 +3539,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96194507</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3501,6 +3641,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96194502</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3598,6 +3743,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96194509</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3714,6 +3864,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135329747</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3825,6 +3980,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330904</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3922,6 +4082,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96194505</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4029,6 +4194,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323512</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4138,6 +4308,11 @@
       <c r="AY35" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330905</t>
         </is>
       </c>
     </row>
@@ -4256,6 +4431,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325992</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4353,6 +4533,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96019446</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4450,6 +4635,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96019447</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4561,6 +4751,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325994</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4658,6 +4853,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96194518</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4755,6 +4955,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96194501</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4852,6 +5057,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96194499</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4949,6 +5159,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96194529</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5046,6 +5261,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96194530</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5157,6 +5377,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135322914</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5268,6 +5493,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135322917</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5379,6 +5609,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135322921</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5490,6 +5725,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135322922</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5601,6 +5841,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325988</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5712,6 +5957,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325991</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5823,6 +6073,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325995</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5934,6 +6189,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325998</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6031,6 +6291,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96019450</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6142,6 +6407,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135322912</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6253,6 +6523,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135322919</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6362,6 +6637,11 @@
       <c r="AY56" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135322924</t>
         </is>
       </c>
     </row>
@@ -6479,6 +6759,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323511</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6586,6 +6871,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323515</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6697,6 +6987,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330907</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6794,6 +7089,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96019466</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6906,6 +7206,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325987</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7018,6 +7323,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325997</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7134,6 +7444,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135329749</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7241,6 +7556,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323517</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7350,6 +7670,11 @@
       <c r="AY65" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325993</t>
         </is>
       </c>
     </row>
@@ -7467,6 +7792,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323508</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7582,6 +7912,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323510</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7692,6 +8027,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135322920</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7793,6 +8133,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96194519</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7916,6 +8261,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323513</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8042,6 +8392,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135322908</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8154,6 +8509,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325985</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8265,6 +8625,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325981</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8376,6 +8741,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135322907</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8487,6 +8857,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325984</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8598,6 +8973,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326431</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8709,6 +9089,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135322909</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8820,6 +9205,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135329744</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8931,6 +9321,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330899</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9043,6 +9438,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325986</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9154,6 +9554,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326430</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9261,8 +9666,96 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323518</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/Maskaure Renskötartjärnen, 8,3 ha artfynd.xlsx
+++ b/artfynd/Maskaure Renskötartjärnen, 8,3 ha artfynd.xlsx
@@ -7436,7 +7436,7 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Moa Turid Lövdahl, per-erik mukka, Johan Råghall</t>
+          <t>Moa Turid Lövdahl, Johan Råghall, per-erik mukka</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">

--- a/artfynd/Maskaure Renskötartjärnen, 8,3 ha artfynd.xlsx
+++ b/artfynd/Maskaure Renskötartjärnen, 8,3 ha artfynd.xlsx
@@ -7436,7 +7436,7 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Moa Turid Lövdahl, Johan Råghall, per-erik mukka</t>
+          <t>Moa Turid Lövdahl, per-erik mukka, Johan Råghall</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">

--- a/artfynd/Maskaure Renskötartjärnen, 8,3 ha artfynd.xlsx
+++ b/artfynd/Maskaure Renskötartjärnen, 8,3 ha artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135322925</v>
       </c>
       <c r="B2" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>135322916</v>
       </c>
       <c r="B17" t="n">
-        <v>92220</v>
+        <v>92262</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         <v>135326001</v>
       </c>
       <c r="B18" t="n">
-        <v>92201</v>
+        <v>92243</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>135322911</v>
       </c>
       <c r="B21" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>135322923</v>
       </c>
       <c r="B22" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>135323509</v>
       </c>
       <c r="B23" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3016,7 +3016,7 @@
         <v>135323514</v>
       </c>
       <c r="B24" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3128,7 +3128,7 @@
         <v>135330900</v>
       </c>
       <c r="B25" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3754,7 +3754,7 @@
         <v>135329747</v>
       </c>
       <c r="B31" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
         <v>135330904</v>
       </c>
       <c r="B32" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
         <v>135323512</v>
       </c>
       <c r="B34" t="n">
-        <v>92027</v>
+        <v>92069</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4205,7 +4205,7 @@
         <v>135330905</v>
       </c>
       <c r="B35" t="n">
-        <v>92027</v>
+        <v>92069</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
         <v>135325992</v>
       </c>
       <c r="B36" t="n">
-        <v>97308</v>
+        <v>97352</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
         <v>135325994</v>
       </c>
       <c r="B39" t="n">
-        <v>91896</v>
+        <v>91938</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>135322914</v>
       </c>
       <c r="B45" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5388,7 +5388,7 @@
         <v>135322917</v>
       </c>
       <c r="B46" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         <v>135322921</v>
       </c>
       <c r="B47" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5620,7 +5620,7 @@
         <v>135322922</v>
       </c>
       <c r="B48" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5736,7 +5736,7 @@
         <v>135325988</v>
       </c>
       <c r="B49" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5852,7 +5852,7 @@
         <v>135325991</v>
       </c>
       <c r="B50" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5968,7 +5968,7 @@
         <v>135325995</v>
       </c>
       <c r="B51" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         <v>135325998</v>
       </c>
       <c r="B52" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6302,7 +6302,7 @@
         <v>135322912</v>
       </c>
       <c r="B54" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6418,7 +6418,7 @@
         <v>135322919</v>
       </c>
       <c r="B55" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6534,7 +6534,7 @@
         <v>135322924</v>
       </c>
       <c r="B56" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6650,7 +6650,7 @@
         <v>135323511</v>
       </c>
       <c r="B57" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6770,7 +6770,7 @@
         <v>135323515</v>
       </c>
       <c r="B58" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6882,7 +6882,7 @@
         <v>135330907</v>
       </c>
       <c r="B59" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7100,7 +7100,7 @@
         <v>135325987</v>
       </c>
       <c r="B61" t="n">
-        <v>78377</v>
+        <v>78415</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         <v>135325997</v>
       </c>
       <c r="B62" t="n">
-        <v>78377</v>
+        <v>78415</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7334,7 +7334,7 @@
         <v>135329749</v>
       </c>
       <c r="B63" t="n">
-        <v>92661</v>
+        <v>92703</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7455,7 +7455,7 @@
         <v>135323517</v>
       </c>
       <c r="B64" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7567,7 +7567,7 @@
         <v>135325993</v>
       </c>
       <c r="B65" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7683,7 +7683,7 @@
         <v>135323508</v>
       </c>
       <c r="B66" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         <v>135323510</v>
       </c>
       <c r="B67" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7923,7 +7923,7 @@
         <v>135322920</v>
       </c>
       <c r="B68" t="n">
-        <v>80267</v>
+        <v>80305</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8144,7 +8144,7 @@
         <v>135323513</v>
       </c>
       <c r="B70" t="n">
-        <v>92222</v>
+        <v>92264</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8272,7 +8272,7 @@
         <v>135322908</v>
       </c>
       <c r="B71" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8403,7 +8403,7 @@
         <v>135325985</v>
       </c>
       <c r="B72" t="n">
-        <v>81355</v>
+        <v>81393</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8520,7 +8520,7 @@
         <v>135325981</v>
       </c>
       <c r="B73" t="n">
-        <v>92027</v>
+        <v>92069</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8636,7 +8636,7 @@
         <v>135322907</v>
       </c>
       <c r="B74" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>135325984</v>
       </c>
       <c r="B75" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8868,7 +8868,7 @@
         <v>135326431</v>
       </c>
       <c r="B76" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8984,7 +8984,7 @@
         <v>135322909</v>
       </c>
       <c r="B77" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
         <v>135329744</v>
       </c>
       <c r="B78" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9216,7 +9216,7 @@
         <v>135330899</v>
       </c>
       <c r="B79" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9332,7 +9332,7 @@
         <v>135325986</v>
       </c>
       <c r="B80" t="n">
-        <v>78377</v>
+        <v>78415</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         <v>135326430</v>
       </c>
       <c r="B81" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9565,7 +9565,7 @@
         <v>135323518</v>
       </c>
       <c r="B82" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>

--- a/artfynd/Maskaure Renskötartjärnen, 8,3 ha artfynd.xlsx
+++ b/artfynd/Maskaure Renskötartjärnen, 8,3 ha artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135322925</v>
       </c>
       <c r="B2" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>135322916</v>
       </c>
       <c r="B17" t="n">
-        <v>92262</v>
+        <v>92289</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         <v>135326001</v>
       </c>
       <c r="B18" t="n">
-        <v>92243</v>
+        <v>92270</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>135322911</v>
       </c>
       <c r="B21" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>135322923</v>
       </c>
       <c r="B22" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>135323509</v>
       </c>
       <c r="B23" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3016,7 +3016,7 @@
         <v>135323514</v>
       </c>
       <c r="B24" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3128,7 +3128,7 @@
         <v>135330900</v>
       </c>
       <c r="B25" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3754,7 +3754,7 @@
         <v>135329747</v>
       </c>
       <c r="B31" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
         <v>135330904</v>
       </c>
       <c r="B32" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
         <v>135323512</v>
       </c>
       <c r="B34" t="n">
-        <v>92069</v>
+        <v>92096</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4205,7 +4205,7 @@
         <v>135330905</v>
       </c>
       <c r="B35" t="n">
-        <v>92069</v>
+        <v>92096</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
         <v>135325992</v>
       </c>
       <c r="B36" t="n">
-        <v>97352</v>
+        <v>97379</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
         <v>135325994</v>
       </c>
       <c r="B39" t="n">
-        <v>91938</v>
+        <v>91965</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>135322914</v>
       </c>
       <c r="B45" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5388,7 +5388,7 @@
         <v>135322917</v>
       </c>
       <c r="B46" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         <v>135322921</v>
       </c>
       <c r="B47" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5620,7 +5620,7 @@
         <v>135322922</v>
       </c>
       <c r="B48" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5736,7 +5736,7 @@
         <v>135325988</v>
       </c>
       <c r="B49" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5852,7 +5852,7 @@
         <v>135325991</v>
       </c>
       <c r="B50" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5968,7 +5968,7 @@
         <v>135325995</v>
       </c>
       <c r="B51" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         <v>135325998</v>
       </c>
       <c r="B52" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6302,7 +6302,7 @@
         <v>135322912</v>
       </c>
       <c r="B54" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6418,7 +6418,7 @@
         <v>135322919</v>
       </c>
       <c r="B55" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6534,7 +6534,7 @@
         <v>135322924</v>
       </c>
       <c r="B56" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6650,7 +6650,7 @@
         <v>135323511</v>
       </c>
       <c r="B57" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6770,7 +6770,7 @@
         <v>135323515</v>
       </c>
       <c r="B58" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6882,7 +6882,7 @@
         <v>135330907</v>
       </c>
       <c r="B59" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7100,7 +7100,7 @@
         <v>135325987</v>
       </c>
       <c r="B61" t="n">
-        <v>78415</v>
+        <v>78442</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         <v>135325997</v>
       </c>
       <c r="B62" t="n">
-        <v>78415</v>
+        <v>78442</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7334,7 +7334,7 @@
         <v>135329749</v>
       </c>
       <c r="B63" t="n">
-        <v>92703</v>
+        <v>92730</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7455,7 +7455,7 @@
         <v>135323517</v>
       </c>
       <c r="B64" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7567,7 +7567,7 @@
         <v>135325993</v>
       </c>
       <c r="B65" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7683,7 +7683,7 @@
         <v>135323508</v>
       </c>
       <c r="B66" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         <v>135323510</v>
       </c>
       <c r="B67" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7923,7 +7923,7 @@
         <v>135322920</v>
       </c>
       <c r="B68" t="n">
-        <v>80305</v>
+        <v>80332</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8144,7 +8144,7 @@
         <v>135323513</v>
       </c>
       <c r="B70" t="n">
-        <v>92264</v>
+        <v>92291</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8272,7 +8272,7 @@
         <v>135322908</v>
       </c>
       <c r="B71" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8403,7 +8403,7 @@
         <v>135325985</v>
       </c>
       <c r="B72" t="n">
-        <v>81393</v>
+        <v>81420</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8520,7 +8520,7 @@
         <v>135325981</v>
       </c>
       <c r="B73" t="n">
-        <v>92069</v>
+        <v>92096</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8636,7 +8636,7 @@
         <v>135322907</v>
       </c>
       <c r="B74" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>135325984</v>
       </c>
       <c r="B75" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8868,7 +8868,7 @@
         <v>135326431</v>
       </c>
       <c r="B76" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8984,7 +8984,7 @@
         <v>135322909</v>
       </c>
       <c r="B77" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
         <v>135329744</v>
       </c>
       <c r="B78" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9216,7 +9216,7 @@
         <v>135330899</v>
       </c>
       <c r="B79" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9332,7 +9332,7 @@
         <v>135325986</v>
       </c>
       <c r="B80" t="n">
-        <v>78415</v>
+        <v>78442</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         <v>135326430</v>
       </c>
       <c r="B81" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9565,7 +9565,7 @@
         <v>135323518</v>
       </c>
       <c r="B82" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>

--- a/artfynd/Maskaure Renskötartjärnen, 8,3 ha artfynd.xlsx
+++ b/artfynd/Maskaure Renskötartjärnen, 8,3 ha artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ33"/>
+  <dimension ref="A1:AZ82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,48 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96194513</v>
+        <v>135322925</v>
       </c>
       <c r="B2" t="n">
-        <v>92841</v>
+        <v>92227</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4745</v>
+        <v>1503</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Seitejaure, Pi lm</t>
+          <t>Renskötartjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>617335</v>
+        <v>617351</v>
       </c>
       <c r="R2" t="n">
-        <v>7315870</v>
+        <v>7315851</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,27 +775,31 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Barbara Kühn, Julian Klein, Björn Mildh, Kristina Bäck, Maj Aspebo</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96194513</t>
+          <t>https://artportalen.se/Sighting/135322925</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96194533</v>
+        <v>96194513</v>
       </c>
       <c r="B3" t="n">
-        <v>78730</v>
+        <v>92841</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +807,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6437</v>
+        <v>4745</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>617343</v>
+        <v>617335</v>
       </c>
       <c r="R3" t="n">
-        <v>7315878</v>
+        <v>7315870</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -878,16 +892,16 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96194533</t>
+          <t>https://artportalen.se/Sighting/96194513</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>96194532</v>
+        <v>96194533</v>
       </c>
       <c r="B4" t="n">
-        <v>78334</v>
+        <v>78730</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +909,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6487</v>
+        <v>6437</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -922,7 +936,7 @@
         <v>617343</v>
       </c>
       <c r="R4" t="n">
-        <v>7315877</v>
+        <v>7315878</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -980,38 +994,38 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96194532</t>
+          <t>https://artportalen.se/Sighting/96194533</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>96194512</v>
+        <v>96194532</v>
       </c>
       <c r="B5" t="n">
-        <v>97983</v>
+        <v>78334</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>6487</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>617351</v>
+        <v>617343</v>
       </c>
       <c r="R5" t="n">
-        <v>7315858</v>
+        <v>7315877</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1082,38 +1096,38 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96194512</t>
+          <t>https://artportalen.se/Sighting/96194532</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>96194523</v>
+        <v>96194512</v>
       </c>
       <c r="B6" t="n">
-        <v>78993</v>
+        <v>97983</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1137,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>617326</v>
+        <v>617351</v>
       </c>
       <c r="R6" t="n">
-        <v>7315927</v>
+        <v>7315858</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1184,16 +1198,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96194523</t>
+          <t>https://artportalen.se/Sighting/96194512</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>96019461</v>
+        <v>96194523</v>
       </c>
       <c r="B7" t="n">
-        <v>91962</v>
+        <v>78993</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,21 +1215,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,13 +1239,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>617355</v>
+        <v>617326</v>
       </c>
       <c r="R7" t="n">
-        <v>7315953</v>
+        <v>7315927</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1275,24 +1289,24 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Julian Klein</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Julian Klein, Barbara Kühn, Björn Mildh, Kristina Bäck, Isak Vahlström, Maj Aspebo</t>
+          <t>Isak Vahlström, Barbara Kühn, Julian Klein, Björn Mildh, Kristina Bäck, Maj Aspebo</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96019461</t>
+          <t>https://artportalen.se/Sighting/96194523</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>96194537</v>
+        <v>96019461</v>
       </c>
       <c r="B8" t="n">
         <v>91962</v>
@@ -1327,13 +1341,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>617330</v>
+        <v>617355</v>
       </c>
       <c r="R8" t="n">
-        <v>7315904</v>
+        <v>7315953</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1377,27 +1391,27 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Julian Klein</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Barbara Kühn, Julian Klein, Björn Mildh, Kristina Bäck, Maj Aspebo</t>
+          <t>Julian Klein, Barbara Kühn, Björn Mildh, Kristina Bäck, Isak Vahlström, Maj Aspebo</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96194537</t>
+          <t>https://artportalen.se/Sighting/96019461</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>96194520</v>
+        <v>96194537</v>
       </c>
       <c r="B9" t="n">
-        <v>91831</v>
+        <v>91962</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1405,21 +1419,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3242</v>
+        <v>2079</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1432,7 +1446,7 @@
         <v>617330</v>
       </c>
       <c r="R9" t="n">
-        <v>7315913</v>
+        <v>7315904</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1490,16 +1504,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96194520</t>
+          <t>https://artportalen.se/Sighting/96194537</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>96194525</v>
+        <v>96194520</v>
       </c>
       <c r="B10" t="n">
-        <v>78730</v>
+        <v>91831</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1507,21 +1521,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6437</v>
+        <v>3242</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1545,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>617275</v>
+        <v>617330</v>
       </c>
       <c r="R10" t="n">
-        <v>7315950</v>
+        <v>7315913</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1592,16 +1606,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96194525</t>
+          <t>https://artportalen.se/Sighting/96194520</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>96019452</v>
+        <v>96194525</v>
       </c>
       <c r="B11" t="n">
-        <v>79946</v>
+        <v>78730</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1609,21 +1623,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,13 +1647,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>617295</v>
+        <v>617275</v>
       </c>
       <c r="R11" t="n">
-        <v>7315943</v>
+        <v>7315950</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1683,24 +1697,24 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Julian Klein</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Julian Klein, Barbara Kühn, Björn Mildh, Kristina Bäck, Isak Vahlström, Maj Aspebo</t>
+          <t>Isak Vahlström, Barbara Kühn, Julian Klein, Björn Mildh, Kristina Bäck, Maj Aspebo</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96019452</t>
+          <t>https://artportalen.se/Sighting/96194525</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>96194522</v>
+        <v>96019452</v>
       </c>
       <c r="B12" t="n">
         <v>79946</v>
@@ -1735,13 +1749,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>617335</v>
+        <v>617295</v>
       </c>
       <c r="R12" t="n">
-        <v>7315916</v>
+        <v>7315943</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1785,24 +1799,24 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Julian Klein</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Barbara Kühn, Julian Klein, Björn Mildh, Kristina Bäck, Maj Aspebo</t>
+          <t>Julian Klein, Barbara Kühn, Björn Mildh, Kristina Bäck, Isak Vahlström, Maj Aspebo</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96194522</t>
+          <t>https://artportalen.se/Sighting/96019452</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>96194534</v>
+        <v>96194522</v>
       </c>
       <c r="B13" t="n">
         <v>79946</v>
@@ -1837,10 +1851,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>617331</v>
+        <v>617335</v>
       </c>
       <c r="R13" t="n">
-        <v>7315887</v>
+        <v>7315916</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1898,16 +1912,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96194534</t>
+          <t>https://artportalen.se/Sighting/96194522</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>96194524</v>
+        <v>96194534</v>
       </c>
       <c r="B14" t="n">
-        <v>78334</v>
+        <v>79946</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1915,21 +1929,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1953,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>617276</v>
+        <v>617331</v>
       </c>
       <c r="R14" t="n">
-        <v>7315951</v>
+        <v>7315887</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2000,38 +2014,38 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96194524</t>
+          <t>https://artportalen.se/Sighting/96194534</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>96019494</v>
+        <v>96194524</v>
       </c>
       <c r="B15" t="n">
-        <v>92183</v>
+        <v>78334</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>65</v>
+        <v>6487</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,13 +2055,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>617519</v>
+        <v>617276</v>
       </c>
       <c r="R15" t="n">
-        <v>7315806</v>
+        <v>7315951</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2091,49 +2105,49 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Julian Klein</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Julian Klein, Barbara Kühn, Björn Mildh, Kristina Bäck, Isak Vahlström, Maj Aspebo</t>
+          <t>Isak Vahlström, Barbara Kühn, Julian Klein, Björn Mildh, Kristina Bäck, Maj Aspebo</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96019494</t>
+          <t>https://artportalen.se/Sighting/96194524</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>96019500</v>
+        <v>96019494</v>
       </c>
       <c r="B16" t="n">
-        <v>78993</v>
+        <v>92183</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>65</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2157,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>617548</v>
+        <v>617519</v>
       </c>
       <c r="R16" t="n">
-        <v>7315810</v>
+        <v>7315806</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2204,54 +2218,54 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96019500</t>
+          <t>https://artportalen.se/Sighting/96019494</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>96194508</v>
+        <v>135322916</v>
       </c>
       <c r="B17" t="n">
-        <v>78993</v>
+        <v>92294</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>65</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Seitejaure, Pi lm</t>
+          <t>Renskötartjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>617483</v>
+        <v>617488</v>
       </c>
       <c r="R17" t="n">
-        <v>7315870</v>
+        <v>7315752</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2275,12 +2289,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2295,27 +2319,31 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Barbara Kühn, Julian Klein, Björn Mildh, Kristina Bäck, Maj Aspebo</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96194508</t>
+          <t>https://artportalen.se/Sighting/135322916</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>96194504</v>
+        <v>135326001</v>
       </c>
       <c r="B18" t="n">
-        <v>91846</v>
+        <v>92275</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2323,37 +2351,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>714</v>
+        <v>67</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tallstocksticka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Osmoporus protractus</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Bondartsev</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Seitejaure, Pi lm</t>
+          <t>Maskaure Renskötartjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>617476</v>
+        <v>617442</v>
       </c>
       <c r="R18" t="n">
-        <v>7315870</v>
+        <v>7315781</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2377,12 +2405,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2391,55 +2429,60 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Barbara Kühn, Julian Klein, Björn Mildh, Kristina Bäck, Maj Aspebo</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96194504</t>
+          <t>https://artportalen.se/Sighting/135326001</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>96019487</v>
+        <v>96019500</v>
       </c>
       <c r="B19" t="n">
-        <v>91923</v>
+        <v>78993</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1204</v>
+        <v>353</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2449,10 +2492,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>617546</v>
+        <v>617548</v>
       </c>
       <c r="R19" t="n">
-        <v>7315805</v>
+        <v>7315810</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2510,38 +2553,38 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96019487</t>
+          <t>https://artportalen.se/Sighting/96019500</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>96194507</v>
+        <v>96194508</v>
       </c>
       <c r="B20" t="n">
-        <v>91923</v>
+        <v>78993</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1204</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2551,7 +2594,7 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>617476</v>
+        <v>617483</v>
       </c>
       <c r="R20" t="n">
         <v>7315870</v>
@@ -2612,54 +2655,54 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96194507</t>
+          <t>https://artportalen.se/Sighting/96194508</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>96194502</v>
+        <v>135322911</v>
       </c>
       <c r="B21" t="n">
-        <v>92083</v>
+        <v>79107</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Seitejaure, Pi lm</t>
+          <t>Renskötartjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>617497</v>
+        <v>617418</v>
       </c>
       <c r="R21" t="n">
-        <v>7315828</v>
+        <v>7315875</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2683,12 +2726,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2703,65 +2756,69 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Barbara Kühn, Julian Klein, Björn Mildh, Kristina Bäck, Maj Aspebo</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96194502</t>
+          <t>https://artportalen.se/Sighting/135322911</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>96194509</v>
+        <v>135322923</v>
       </c>
       <c r="B22" t="n">
-        <v>92083</v>
+        <v>79107</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Seitejaure, Pi lm</t>
+          <t>Renskötartjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>617398</v>
+        <v>617395</v>
       </c>
       <c r="R22" t="n">
-        <v>7315856</v>
+        <v>7315778</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2785,12 +2842,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2805,27 +2872,31 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Barbara Kühn, Julian Klein, Björn Mildh, Kristina Bäck, Maj Aspebo</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96194509</t>
+          <t>https://artportalen.se/Sighting/135322923</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>96194505</v>
+        <v>135323509</v>
       </c>
       <c r="B23" t="n">
-        <v>91962</v>
+        <v>79107</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2833,37 +2904,40 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Seitejaure, Pi lm</t>
+          <t>Maskaure Långmyran SV + Renskötartjärnen_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>617476</v>
+        <v>617488</v>
       </c>
       <c r="R23" t="n">
-        <v>7315870</v>
+        <v>7315863</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2887,12 +2961,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2901,33 +2985,38 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Barbara Kühn, Julian Klein, Björn Mildh, Kristina Bäck, Maj Aspebo</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96194505</t>
+          <t>https://artportalen.se/Sighting/135323509</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>96019446</v>
+        <v>135323514</v>
       </c>
       <c r="B24" t="n">
-        <v>91831</v>
+        <v>79107</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2935,37 +3024,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3242</v>
+        <v>353</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Seitejaure, Pi lm</t>
+          <t>Maskaure Långmyran SV + Renskötartjärnen_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>617558</v>
+        <v>617617</v>
       </c>
       <c r="R24" t="n">
-        <v>7315745</v>
+        <v>7315754</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2989,12 +3078,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3009,27 +3108,27 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Julian Klein</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Julian Klein, Barbara Kühn, Björn Mildh, Kristina Bäck, Isak Vahlström, Maj Aspebo</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96019446</t>
+          <t>https://artportalen.se/Sighting/135323514</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>96019447</v>
+        <v>135330900</v>
       </c>
       <c r="B25" t="n">
-        <v>91831</v>
+        <v>79107</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3037,37 +3136,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3242</v>
+        <v>353</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Seitejaure, Pi lm</t>
+          <t>Maskaure Långmyran SV + Renskötartjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>617402</v>
+        <v>617490</v>
       </c>
       <c r="R25" t="n">
-        <v>7315828</v>
+        <v>7315847</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3091,12 +3190,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3111,27 +3220,31 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Julian Klein</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Julian Klein, Barbara Kühn, Björn Mildh, Kristina Bäck, Isak Vahlström, Maj Aspebo</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
+          <t>Elin Kannerby, Johan Råghall, Cecilia Goldkuhl, per-erik mukka, Christina Boyd, Moa Turid Lövdahl</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96019447</t>
+          <t>https://artportalen.se/Sighting/135330900</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>96194518</v>
+        <v>96194504</v>
       </c>
       <c r="B26" t="n">
-        <v>93201</v>
+        <v>91846</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3139,21 +3252,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4365</v>
+        <v>714</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Tallstocksticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Osmoporus protractus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3163,10 +3276,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>617390</v>
+        <v>617476</v>
       </c>
       <c r="R26" t="n">
-        <v>7315768</v>
+        <v>7315870</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3224,38 +3337,38 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96194518</t>
+          <t>https://artportalen.se/Sighting/96194504</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>96194501</v>
+        <v>96019487</v>
       </c>
       <c r="B27" t="n">
-        <v>93209</v>
+        <v>91923</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4366</v>
+        <v>1204</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3265,13 +3378,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>617535</v>
+        <v>617546</v>
       </c>
       <c r="R27" t="n">
-        <v>7315839</v>
+        <v>7315805</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3315,49 +3428,49 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Julian Klein</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Barbara Kühn, Julian Klein, Björn Mildh, Kristina Bäck, Maj Aspebo</t>
+          <t>Julian Klein, Barbara Kühn, Björn Mildh, Kristina Bäck, Isak Vahlström, Maj Aspebo</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96194501</t>
+          <t>https://artportalen.se/Sighting/96019487</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>96194499</v>
+        <v>96194507</v>
       </c>
       <c r="B28" t="n">
-        <v>78730</v>
+        <v>91923</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6437</v>
+        <v>1204</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3367,10 +3480,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>617540</v>
+        <v>617476</v>
       </c>
       <c r="R28" t="n">
-        <v>7315810</v>
+        <v>7315870</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3428,38 +3541,38 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96194499</t>
+          <t>https://artportalen.se/Sighting/96194507</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>96194529</v>
+        <v>96194502</v>
       </c>
       <c r="B29" t="n">
-        <v>78730</v>
+        <v>92083</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6437</v>
+        <v>1503</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3469,10 +3582,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>617391</v>
+        <v>617497</v>
       </c>
       <c r="R29" t="n">
-        <v>7315876</v>
+        <v>7315828</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3530,38 +3643,38 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96194529</t>
+          <t>https://artportalen.se/Sighting/96194502</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>96194530</v>
+        <v>96194509</v>
       </c>
       <c r="B30" t="n">
-        <v>78730</v>
+        <v>92083</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6437</v>
+        <v>1503</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3571,10 +3684,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>617368</v>
+        <v>617398</v>
       </c>
       <c r="R30" t="n">
-        <v>7315854</v>
+        <v>7315856</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3632,54 +3745,54 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96194530</t>
+          <t>https://artportalen.se/Sighting/96194509</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>96019450</v>
+        <v>135329747</v>
       </c>
       <c r="B31" t="n">
-        <v>79946</v>
+        <v>92227</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>1503</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Seitejaure, Pi lm</t>
+          <t>_Maskaure Långmyran SV + Renskötartjärnen_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>617512</v>
+        <v>617572</v>
       </c>
       <c r="R31" t="n">
-        <v>7315786</v>
+        <v>7315630</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3703,12 +3816,27 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Tallåga</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3723,65 +3851,69 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Julian Klein</t>
+          <t>Moa Turid Lövdahl</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Julian Klein, Barbara Kühn, Björn Mildh, Kristina Bäck, Isak Vahlström, Maj Aspebo</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr"/>
+          <t>Moa Turid Lövdahl</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96019450</t>
+          <t>https://artportalen.se/Sighting/135329747</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>96019466</v>
+        <v>135330904</v>
       </c>
       <c r="B32" t="n">
-        <v>80468</v>
+        <v>92227</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6464</v>
+        <v>1503</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Seitejaure, Pi lm</t>
+          <t>Maskaure Långmyran SV + Renskötartjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>617633</v>
+        <v>617575</v>
       </c>
       <c r="R32" t="n">
-        <v>7315774</v>
+        <v>7315628</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3805,12 +3937,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3825,65 +3967,66 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Julian Klein</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Julian Klein, Barbara Kühn, Björn Mildh, Kristina Bäck, Isak Vahlström, Maj Aspebo</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr"/>
+          <t>Elin Kannerby, Johan Råghall, Cecilia Goldkuhl, per-erik mukka, Christina Boyd, Moa Turid Lövdahl</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96019466</t>
+          <t>https://artportalen.se/Sighting/135330904</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>96194519</v>
+        <v>96194505</v>
       </c>
       <c r="B33" t="n">
-        <v>92185</v>
+        <v>91962</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6008693</v>
+        <v>2079</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kritporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Antrodia crassa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Seitejaure, Pi lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>617621</v>
+        <v>617476</v>
       </c>
       <c r="R33" t="n">
-        <v>7315742</v>
+        <v>7315870</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3924,7 +4067,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3942,7 +4084,5591 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/96194505</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>135323512</v>
+      </c>
+      <c r="B34" t="n">
+        <v>92101</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Maskaure Långmyran SV + Renskötartjärnen_topo, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>617601</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7315777</v>
+      </c>
+      <c r="S34" t="n">
+        <v>6</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323512</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>135330905</v>
+      </c>
+      <c r="B35" t="n">
+        <v>92101</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Maskaure Långmyran SV + Renskötartjärnen, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>617574</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7315632</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Johan Råghall, Cecilia Goldkuhl, per-erik mukka, Christina Boyd, Moa Turid Lövdahl</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330905</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>135325992</v>
+      </c>
+      <c r="B36" t="n">
+        <v>97384</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>2869</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Bollvitmossa</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Sphagnum wulfianum</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Maskaure Renskötartjärnen, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>617462</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7315746</v>
+      </c>
+      <c r="S36" t="n">
+        <v>9</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325992</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>96019446</v>
+      </c>
+      <c r="B37" t="n">
+        <v>91831</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>3242</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Vitplätt</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Chaetodermella luna</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Seitejaure, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>617558</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7315745</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2021-09-10</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2021-09-10</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Julian Klein</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Julian Klein, Barbara Kühn, Björn Mildh, Kristina Bäck, Isak Vahlström, Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96019446</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>96019447</v>
+      </c>
+      <c r="B38" t="n">
+        <v>91831</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>3242</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Vitplätt</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Chaetodermella luna</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Seitejaure, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>617402</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7315828</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2021-09-10</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2021-09-10</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Julian Klein</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Julian Klein, Barbara Kühn, Björn Mildh, Kristina Bäck, Isak Vahlström, Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96019447</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>135325994</v>
+      </c>
+      <c r="B39" t="n">
+        <v>91970</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>3242</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Vitplätt</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Chaetodermella luna</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Maskaure Renskötartjärnen, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>617554</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7315710</v>
+      </c>
+      <c r="S39" t="n">
+        <v>8</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325994</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>96194518</v>
+      </c>
+      <c r="B40" t="n">
+        <v>93201</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>4365</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Smalfotad taggsvamp</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Hydnellum gracilipes</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Seitejaure, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>617390</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7315768</v>
+      </c>
+      <c r="S40" t="n">
+        <v>25</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2021-09-10</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2021-09-10</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Barbara Kühn, Julian Klein, Björn Mildh, Kristina Bäck, Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96194518</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>96194501</v>
+      </c>
+      <c r="B41" t="n">
+        <v>93209</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Seitejaure, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>617535</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7315839</v>
+      </c>
+      <c r="S41" t="n">
+        <v>25</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2021-09-10</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2021-09-10</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Barbara Kühn, Julian Klein, Björn Mildh, Kristina Bäck, Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96194501</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>96194499</v>
+      </c>
+      <c r="B42" t="n">
+        <v>78730</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Seitejaure, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>617540</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7315810</v>
+      </c>
+      <c r="S42" t="n">
+        <v>25</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2021-09-10</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2021-09-10</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Barbara Kühn, Julian Klein, Björn Mildh, Kristina Bäck, Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96194499</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>96194529</v>
+      </c>
+      <c r="B43" t="n">
+        <v>78730</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Seitejaure, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>617391</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7315876</v>
+      </c>
+      <c r="S43" t="n">
+        <v>25</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2021-09-10</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2021-09-10</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Barbara Kühn, Julian Klein, Björn Mildh, Kristina Bäck, Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96194529</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>96194530</v>
+      </c>
+      <c r="B44" t="n">
+        <v>78730</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Seitejaure, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>617368</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7315854</v>
+      </c>
+      <c r="S44" t="n">
+        <v>25</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2021-09-10</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2021-09-10</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Barbara Kühn, Julian Klein, Björn Mildh, Kristina Bäck, Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96194530</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>135322914</v>
+      </c>
+      <c r="B45" t="n">
+        <v>78844</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Renskötartjärnen, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>617556</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7315832</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135322914</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>135322917</v>
+      </c>
+      <c r="B46" t="n">
+        <v>78844</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Renskötartjärnen, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>617543</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7315687</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135322917</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>135322921</v>
+      </c>
+      <c r="B47" t="n">
+        <v>78844</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Renskötartjärnen, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>617551</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7315614</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135322921</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>135322922</v>
+      </c>
+      <c r="B48" t="n">
+        <v>78844</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Renskötartjärnen, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>617446</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7315745</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135322922</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>135325988</v>
+      </c>
+      <c r="B49" t="n">
+        <v>78844</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Maskaure Renskötartjärnen, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>617426</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7315822</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325988</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>135325991</v>
+      </c>
+      <c r="B50" t="n">
+        <v>78844</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Maskaure Renskötartjärnen, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>617467</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7315790</v>
+      </c>
+      <c r="S50" t="n">
+        <v>8</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325991</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>135325995</v>
+      </c>
+      <c r="B51" t="n">
+        <v>78844</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Maskaure Renskötartjärnen, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>617544</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7315719</v>
+      </c>
+      <c r="S51" t="n">
+        <v>9</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325995</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>135325998</v>
+      </c>
+      <c r="B52" t="n">
+        <v>78844</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Maskaure Renskötartjärnen, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>617566</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7315680</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325998</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>96019450</v>
+      </c>
+      <c r="B53" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Seitejaure, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>617512</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7315786</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2021-09-10</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2021-09-10</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Julian Klein</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Julian Klein, Barbara Kühn, Björn Mildh, Kristina Bäck, Isak Vahlström, Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96019450</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>135322912</v>
+      </c>
+      <c r="B54" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Renskötartjärnen, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>617490</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7315847</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135322912</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>135322919</v>
+      </c>
+      <c r="B55" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Renskötartjärnen, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>617575</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7315656</v>
+      </c>
+      <c r="S55" t="n">
+        <v>5</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135322919</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>135322924</v>
+      </c>
+      <c r="B56" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Renskötartjärnen, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>617370</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7315842</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135322924</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>135323511</v>
+      </c>
+      <c r="B57" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Maskaure Långmyran SV + Renskötartjärnen_topo, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>617584</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7315763</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323511</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>135323515</v>
+      </c>
+      <c r="B58" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Maskaure Långmyran SV + Renskötartjärnen_topo, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>617465</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7315657</v>
+      </c>
+      <c r="S58" t="n">
+        <v>5</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323515</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>135330907</v>
+      </c>
+      <c r="B59" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Maskaure Långmyran SV + Renskötartjärnen, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>617555</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7315587</v>
+      </c>
+      <c r="S59" t="n">
+        <v>24</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Johan Råghall, Cecilia Goldkuhl, per-erik mukka, Christina Boyd, Moa Turid Lövdahl</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330907</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>96019466</v>
+      </c>
+      <c r="B60" t="n">
+        <v>80468</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Seitejaure, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>617633</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7315774</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2021-09-10</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2021-09-10</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Julian Klein</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Julian Klein, Barbara Kühn, Björn Mildh, Kristina Bäck, Isak Vahlström, Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96019466</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>135325987</v>
+      </c>
+      <c r="B61" t="n">
+        <v>78445</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Maskaure Renskötartjärnen, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>617425</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7315818</v>
+      </c>
+      <c r="S61" t="n">
+        <v>5</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325987</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>135325997</v>
+      </c>
+      <c r="B62" t="n">
+        <v>78445</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Maskaure Renskötartjärnen, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>617566</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7315680</v>
+      </c>
+      <c r="S62" t="n">
+        <v>5</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325997</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>135329749</v>
+      </c>
+      <c r="B63" t="n">
+        <v>92735</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>106596</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Nordlig parasitporing</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Antrodiella pallasii</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Renvall &amp; al.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>_Maskaure Långmyran SV + Renskötartjärnen_topo, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>617541</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7315552</v>
+      </c>
+      <c r="S63" t="n">
+        <v>5</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ganska nedbruten granlåga</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Moa Turid Lövdahl</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Moa Turid Lövdahl, per-erik mukka, Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135329749</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>135323517</v>
+      </c>
+      <c r="B64" t="n">
+        <v>98142</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Maskaure Långmyran SV + Renskötartjärnen_topo, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>617470</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7315735</v>
+      </c>
+      <c r="S64" t="n">
+        <v>5</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323517</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>135325993</v>
+      </c>
+      <c r="B65" t="n">
+        <v>98142</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Maskaure Renskötartjärnen, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>617460</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7315781</v>
+      </c>
+      <c r="S65" t="n">
+        <v>5</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325993</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>135323508</v>
+      </c>
+      <c r="B66" t="n">
+        <v>79464</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Maskaure Långmyran SV + Renskötartjärnen_topo, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>617490</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7315864</v>
+      </c>
+      <c r="S66" t="n">
+        <v>8</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323508</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>135323510</v>
+      </c>
+      <c r="B67" t="n">
+        <v>79464</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Maskaure Långmyran SV + Renskötartjärnen_topo, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>617539</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7315769</v>
+      </c>
+      <c r="S67" t="n">
+        <v>5</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF67" t="inlineStr"/>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323510</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>135322920</v>
+      </c>
+      <c r="B68" t="n">
+        <v>80335</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>266179</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Lecidea subhumida</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Vain.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Renskötartjärnen, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>617594</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7315642</v>
+      </c>
+      <c r="S68" t="n">
+        <v>21</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135322920</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>96194519</v>
+      </c>
+      <c r="B69" t="n">
+        <v>92185</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>6008693</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Kritporing</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Antrodia crassa</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Ryvarden</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Seitejaure, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>617621</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7315742</v>
+      </c>
+      <c r="S69" t="n">
+        <v>25</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2021-09-10</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2021-09-10</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Barbara Kühn, Julian Klein, Björn Mildh, Kristina Bäck, Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/96194519</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>135323513</v>
+      </c>
+      <c r="B70" t="n">
+        <v>92296</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>6008693</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Kritporing</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Antrodia crassa</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Ryvarden</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Maskaure Långmyran SV + Renskötartjärnen_topo, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>617623</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7315761</v>
+      </c>
+      <c r="S70" t="n">
+        <v>5</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF70" t="inlineStr"/>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl, per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323513</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>135322908</v>
+      </c>
+      <c r="B71" t="n">
+        <v>79520</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>864</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Knottrig blåslav</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Hypogymnia bitteri</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Renskötartjärnen, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>617413</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7315903</v>
+      </c>
+      <c r="S71" t="n">
+        <v>5</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135322908</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>135325985</v>
+      </c>
+      <c r="B72" t="n">
+        <v>81423</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>1049</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Microcalicium ahlneri</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Maskaure Renskötartjärnen, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>617385</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7315903</v>
+      </c>
+      <c r="S72" t="n">
+        <v>5</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF72" t="inlineStr"/>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325985</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>135325981</v>
+      </c>
+      <c r="B73" t="n">
+        <v>92101</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Maskaure Renskötartjärnen, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>617398</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7315912</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325981</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>135322907</v>
+      </c>
+      <c r="B74" t="n">
+        <v>78844</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Renskötartjärnen, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>617410</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7315918</v>
+      </c>
+      <c r="S74" t="n">
+        <v>6</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135322907</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>135325984</v>
+      </c>
+      <c r="B75" t="n">
+        <v>78844</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Maskaure Renskötartjärnen, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>617385</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7315903</v>
+      </c>
+      <c r="S75" t="n">
+        <v>5</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325984</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>135326431</v>
+      </c>
+      <c r="B76" t="n">
+        <v>78844</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_topo, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>617403</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7315880</v>
+      </c>
+      <c r="S76" t="n">
+        <v>8</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326431</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>135322909</v>
+      </c>
+      <c r="B77" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Renskötartjärnen, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>617413</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7315903</v>
+      </c>
+      <c r="S77" t="n">
+        <v>5</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135322909</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>135329744</v>
+      </c>
+      <c r="B78" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>_Maskaure Långmyran SV + Renskötartjärnen_topo, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>617411</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7315912</v>
+      </c>
+      <c r="S78" t="n">
+        <v>5</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Moa Turid Lövdahl</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Moa Turid Lövdahl</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135329744</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>135330899</v>
+      </c>
+      <c r="B79" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Maskaure Långmyran SV + Renskötartjärnen, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>617384</v>
+      </c>
+      <c r="R79" t="n">
+        <v>7315902</v>
+      </c>
+      <c r="S79" t="n">
+        <v>13</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Johan Råghall, Cecilia Goldkuhl, per-erik mukka, Christina Boyd, Moa Turid Lövdahl</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330899</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>135325986</v>
+      </c>
+      <c r="B80" t="n">
+        <v>78445</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Maskaure Renskötartjärnen, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>617385</v>
+      </c>
+      <c r="R80" t="n">
+        <v>7315903</v>
+      </c>
+      <c r="S80" t="n">
+        <v>5</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF80" t="inlineStr"/>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325986</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>135326430</v>
+      </c>
+      <c r="B81" t="n">
+        <v>79199</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Ons Gr 3_Maskaure Långmyran SV + Renskötartjärnen_topo, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>617403</v>
+      </c>
+      <c r="R81" t="n">
+        <v>7315880</v>
+      </c>
+      <c r="S81" t="n">
+        <v>8</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326430</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>135323518</v>
+      </c>
+      <c r="B82" t="n">
+        <v>79464</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Maskaure Långmyran SV + Renskötartjärnen_topo, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>617376</v>
+      </c>
+      <c r="R82" t="n">
+        <v>7315923</v>
+      </c>
+      <c r="S82" t="n">
+        <v>5</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323518</t>
         </is>
       </c>
     </row>
@@ -3980,6 +9706,55 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/Maskaure Renskötartjärnen, 8,3 ha artfynd.xlsx
+++ b/artfynd/Maskaure Renskötartjärnen, 8,3 ha artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135322925</v>
       </c>
       <c r="B2" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>135322916</v>
       </c>
       <c r="B17" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         <v>135326001</v>
       </c>
       <c r="B18" t="n">
-        <v>92275</v>
+        <v>92277</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3754,7 +3754,7 @@
         <v>135329747</v>
       </c>
       <c r="B31" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
         <v>135330904</v>
       </c>
       <c r="B32" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
         <v>135323512</v>
       </c>
       <c r="B34" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4205,7 +4205,7 @@
         <v>135330905</v>
       </c>
       <c r="B35" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
         <v>135325992</v>
       </c>
       <c r="B36" t="n">
-        <v>97384</v>
+        <v>97386</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
         <v>135325994</v>
       </c>
       <c r="B39" t="n">
-        <v>91970</v>
+        <v>91972</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -7334,7 +7334,7 @@
         <v>135329749</v>
       </c>
       <c r="B63" t="n">
-        <v>92735</v>
+        <v>92737</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7455,7 +7455,7 @@
         <v>135323517</v>
       </c>
       <c r="B64" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7567,7 +7567,7 @@
         <v>135325993</v>
       </c>
       <c r="B65" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8144,7 +8144,7 @@
         <v>135323513</v>
       </c>
       <c r="B70" t="n">
-        <v>92296</v>
+        <v>92298</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8520,7 +8520,7 @@
         <v>135325981</v>
       </c>
       <c r="B73" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>

--- a/artfynd/Maskaure Renskötartjärnen, 8,3 ha artfynd.xlsx
+++ b/artfynd/Maskaure Renskötartjärnen, 8,3 ha artfynd.xlsx
@@ -7334,7 +7334,7 @@
         <v>135329749</v>
       </c>
       <c r="B63" t="n">
-        <v>92737</v>
+        <v>92752</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
